--- a/data_lake/metadata.xlsx
+++ b/data_lake/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBBDAC0-B351-4736-83B2-6978D11342D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21400" yWindow="5280" windowWidth="29040" windowHeight="19540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -14036,28 +14036,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -14065,7 +14065,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -14109,7 +14109,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -14140,37 +14140,37 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -14449,26 +14449,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O858"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="5"/>
-    <col min="2" max="2" width="12.59765625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="5"/>
+    <col min="2" max="2" width="12.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.19921875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="6" customWidth="1"/>
     <col min="10" max="10" width="43" style="6" customWidth="1"/>
-    <col min="11" max="11" width="31.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.796875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="31.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.83203125" style="6" customWidth="1"/>
     <col min="14" max="14" width="16.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.796875" style="6"/>
-    <col min="16" max="16384" width="8.796875" style="5"/>
+    <col min="15" max="15" width="8.83203125" style="6"/>
+    <col min="16" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="3" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" ht="17">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="17">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="17">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ht="17">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -14691,7 +14691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" ht="17">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -14735,7 +14735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" ht="17">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" ht="17">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -14823,7 +14823,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" ht="17">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" ht="17">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -14911,7 +14911,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" ht="17">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -14996,7 +14996,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" ht="17">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" ht="17">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" ht="17">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" ht="17">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -15172,7 +15172,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -15254,7 +15254,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" ht="17">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -15298,7 +15298,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -15339,7 +15339,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" ht="17">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -15383,7 +15383,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" ht="17">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -15427,7 +15427,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" ht="17">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" ht="17">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -15515,7 +15515,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" ht="17">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -15559,7 +15559,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="17">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -15644,7 +15644,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -15685,7 +15685,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" ht="17">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -15729,7 +15729,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" ht="17">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" ht="17">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -15858,7 +15858,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="17">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14" ht="17">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -15946,7 +15946,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14" ht="17">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -15990,7 +15990,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" ht="17">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -16034,7 +16034,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" ht="17">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -16078,7 +16078,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" ht="17">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -16204,7 +16204,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" ht="17">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -16289,7 +16289,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" ht="17">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -16333,7 +16333,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" ht="17">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" ht="17">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -16421,7 +16421,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" ht="17">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -16465,7 +16465,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" ht="17">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -16509,7 +16509,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" ht="17">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -16553,7 +16553,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" ht="17">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" ht="17">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -16682,7 +16682,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -16723,7 +16723,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" ht="17">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -16808,7 +16808,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -16931,7 +16931,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -16972,7 +16972,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:14" ht="17">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:14" ht="17">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -17054,7 +17054,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -17130,7 +17130,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -17168,7 +17168,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -17206,7 +17206,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -17244,7 +17244,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -17282,7 +17282,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -17399,7 +17399,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -17440,7 +17440,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -17522,7 +17522,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -17680,7 +17680,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -17762,7 +17762,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -17800,7 +17800,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -17876,7 +17876,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -17990,7 +17990,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -18066,7 +18066,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -18104,7 +18104,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -18142,7 +18142,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -18180,7 +18180,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -18218,7 +18218,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -18259,7 +18259,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -18335,7 +18335,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -18376,7 +18376,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -18455,7 +18455,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -18493,7 +18493,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -18531,7 +18531,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -18569,7 +18569,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -18645,7 +18645,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -18683,7 +18683,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -18721,7 +18721,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -18797,7 +18797,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -18835,7 +18835,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -18873,7 +18873,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -18911,7 +18911,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -18949,7 +18949,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -18987,7 +18987,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -19025,7 +19025,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -19063,7 +19063,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -19101,7 +19101,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -19139,7 +19139,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -19177,7 +19177,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -19215,7 +19215,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -19253,7 +19253,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -19291,7 +19291,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -19329,7 +19329,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -19367,7 +19367,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -19405,7 +19405,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -19446,7 +19446,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -19481,7 +19481,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -19516,7 +19516,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -19586,7 +19586,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -19621,7 +19621,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -19697,7 +19697,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -19732,7 +19732,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -19805,7 +19805,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -19846,7 +19846,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -19884,7 +19884,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -20039,7 +20039,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -20077,7 +20077,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -20153,7 +20153,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -20191,7 +20191,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -20270,7 +20270,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -20308,7 +20308,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -20384,7 +20384,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -20425,7 +20425,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -20504,7 +20504,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -20545,7 +20545,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -20586,7 +20586,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -20630,7 +20630,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -20668,7 +20668,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -20706,7 +20706,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -20744,7 +20744,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -20782,7 +20782,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -20864,7 +20864,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -20902,7 +20902,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -20940,7 +20940,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -20978,7 +20978,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -21016,7 +21016,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -21130,7 +21130,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -21212,7 +21212,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15">
       <c r="A169" s="5">
         <v>168</v>
       </c>
@@ -21250,7 +21250,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15">
       <c r="A170" s="5">
         <v>169</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15">
       <c r="A171" s="5">
         <v>170</v>
       </c>
@@ -21326,7 +21326,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15">
       <c r="A172" s="5">
         <v>171</v>
       </c>
@@ -21364,7 +21364,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15">
       <c r="A173" s="5">
         <v>172</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15">
       <c r="A174" s="5">
         <v>173</v>
       </c>
@@ -21440,7 +21440,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15">
       <c r="A175" s="5">
         <v>174</v>
       </c>
@@ -21478,7 +21478,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15">
       <c r="A176" s="5">
         <v>175</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15">
       <c r="A177" s="5">
         <v>176</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15">
       <c r="A178" s="5">
         <v>177</v>
       </c>
@@ -21601,7 +21601,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15">
       <c r="A179" s="5">
         <v>178</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15">
       <c r="A180" s="5">
         <v>179</v>
       </c>
@@ -21683,7 +21683,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15">
       <c r="A181" s="5">
         <v>180</v>
       </c>
@@ -21724,7 +21724,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15">
       <c r="A182" s="5">
         <v>181</v>
       </c>
@@ -21765,7 +21765,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15">
       <c r="A183" s="5">
         <v>182</v>
       </c>
@@ -21806,7 +21806,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -21847,7 +21847,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -22052,7 +22052,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -22093,7 +22093,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -22169,7 +22169,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -22207,7 +22207,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -22245,7 +22245,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -22283,7 +22283,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -22321,7 +22321,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -22359,7 +22359,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -22397,7 +22397,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -22435,7 +22435,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -22511,7 +22511,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -22549,7 +22549,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -22587,7 +22587,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -22625,7 +22625,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -22663,7 +22663,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -22701,7 +22701,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -22739,7 +22739,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -22777,7 +22777,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -22853,7 +22853,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -22891,7 +22891,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -22929,7 +22929,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -23005,7 +23005,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -23043,7 +23043,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -23081,7 +23081,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -23119,7 +23119,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -23157,7 +23157,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -23195,7 +23195,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -23233,7 +23233,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -23309,7 +23309,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -23347,7 +23347,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -23423,7 +23423,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15">
       <c r="A226" s="5">
         <v>225</v>
       </c>
@@ -23461,7 +23461,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15">
       <c r="A227" s="5">
         <v>226</v>
       </c>
@@ -23499,7 +23499,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15">
       <c r="A228" s="5">
         <v>227</v>
       </c>
@@ -23537,7 +23537,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15">
       <c r="A229" s="5">
         <v>228</v>
       </c>
@@ -23575,7 +23575,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15">
       <c r="A230" s="5">
         <v>229</v>
       </c>
@@ -23613,7 +23613,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15">
       <c r="A231" s="5">
         <v>230</v>
       </c>
@@ -23651,7 +23651,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15">
       <c r="A232" s="5">
         <v>231</v>
       </c>
@@ -23689,7 +23689,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15">
       <c r="A233" s="5">
         <v>232</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15">
       <c r="A234" s="5">
         <v>233</v>
       </c>
@@ -23765,7 +23765,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15">
       <c r="A235" s="5">
         <v>234</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15">
       <c r="A236" s="5">
         <v>235</v>
       </c>
@@ -23841,7 +23841,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15">
       <c r="A237" s="5">
         <v>236</v>
       </c>
@@ -23879,7 +23879,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15">
       <c r="A238" s="5">
         <v>237</v>
       </c>
@@ -23917,7 +23917,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15">
       <c r="A239" s="5">
         <v>238</v>
       </c>
@@ -23955,7 +23955,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15">
       <c r="A240" s="5">
         <v>239</v>
       </c>
@@ -23993,7 +23993,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15">
       <c r="A241" s="5">
         <v>240</v>
       </c>
@@ -24031,7 +24031,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15">
       <c r="A242" s="5">
         <v>241</v>
       </c>
@@ -24069,7 +24069,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15">
       <c r="A243" s="5">
         <v>242</v>
       </c>
@@ -24107,7 +24107,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15">
       <c r="A244" s="5">
         <v>243</v>
       </c>
@@ -24145,7 +24145,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15">
       <c r="A245" s="5">
         <v>244</v>
       </c>
@@ -24183,7 +24183,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15">
       <c r="A246" s="5">
         <v>245</v>
       </c>
@@ -24221,7 +24221,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15">
       <c r="A247" s="5">
         <v>246</v>
       </c>
@@ -24259,7 +24259,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15">
       <c r="A248" s="5">
         <v>247</v>
       </c>
@@ -24297,7 +24297,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15">
       <c r="A249" s="5">
         <v>248</v>
       </c>
@@ -24335,7 +24335,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15">
       <c r="A250" s="5">
         <v>249</v>
       </c>
@@ -24373,7 +24373,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15">
       <c r="A251" s="5">
         <v>250</v>
       </c>
@@ -24411,7 +24411,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15">
       <c r="A252" s="5">
         <v>251</v>
       </c>
@@ -24449,7 +24449,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15">
       <c r="A253" s="5">
         <v>252</v>
       </c>
@@ -24487,7 +24487,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -24525,7 +24525,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -24563,7 +24563,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -24601,7 +24601,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15">
       <c r="A257" s="5">
         <v>256</v>
       </c>
@@ -24639,7 +24639,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -24677,7 +24677,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -24715,7 +24715,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -24753,7 +24753,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -24791,7 +24791,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -24829,7 +24829,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -24867,7 +24867,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -24905,7 +24905,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -24943,7 +24943,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -24981,7 +24981,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -25019,7 +25019,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -25057,7 +25057,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -25095,7 +25095,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -25133,7 +25133,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -25171,7 +25171,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -25209,7 +25209,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -25247,7 +25247,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -25285,7 +25285,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -25323,7 +25323,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -25361,7 +25361,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -25399,7 +25399,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -25437,7 +25437,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -25475,7 +25475,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -25513,7 +25513,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -25551,7 +25551,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -25589,7 +25589,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -25627,7 +25627,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -25665,7 +25665,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -25703,7 +25703,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15">
       <c r="A286" s="5">
         <v>285</v>
       </c>
@@ -25741,7 +25741,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15">
       <c r="A287" s="5">
         <v>286</v>
       </c>
@@ -25779,7 +25779,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15">
       <c r="A288" s="5">
         <v>287</v>
       </c>
@@ -25817,7 +25817,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15">
       <c r="A289" s="5">
         <v>288</v>
       </c>
@@ -25855,7 +25855,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15">
       <c r="A290" s="5">
         <v>289</v>
       </c>
@@ -25893,7 +25893,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15">
       <c r="A291" s="5">
         <v>290</v>
       </c>
@@ -25931,7 +25931,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15">
       <c r="A292" s="5">
         <v>291</v>
       </c>
@@ -25969,7 +25969,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15">
       <c r="A293" s="5">
         <v>292</v>
       </c>
@@ -26007,7 +26007,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15">
       <c r="A294" s="5">
         <v>293</v>
       </c>
@@ -26048,7 +26048,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15">
       <c r="A295" s="5">
         <v>294</v>
       </c>
@@ -26089,7 +26089,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15">
       <c r="A296" s="5">
         <v>295</v>
       </c>
@@ -26130,7 +26130,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15">
       <c r="A297" s="5">
         <v>296</v>
       </c>
@@ -26171,7 +26171,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15">
       <c r="A298" s="5">
         <v>297</v>
       </c>
@@ -26212,7 +26212,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15">
       <c r="A299" s="5">
         <v>298</v>
       </c>
@@ -26253,7 +26253,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15">
       <c r="A300" s="5">
         <v>299</v>
       </c>
@@ -26294,7 +26294,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15">
       <c r="A301" s="5">
         <v>300</v>
       </c>
@@ -26335,7 +26335,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15">
       <c r="A302" s="5">
         <v>301</v>
       </c>
@@ -26376,7 +26376,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15">
       <c r="A303" s="5">
         <v>302</v>
       </c>
@@ -26417,7 +26417,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15">
       <c r="A304" s="5">
         <v>303</v>
       </c>
@@ -26458,7 +26458,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15">
       <c r="A305" s="5">
         <v>304</v>
       </c>
@@ -26499,7 +26499,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15">
       <c r="A306" s="5">
         <v>305</v>
       </c>
@@ -26540,7 +26540,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15">
       <c r="A307" s="5">
         <v>306</v>
       </c>
@@ -26578,7 +26578,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15">
       <c r="A308" s="5">
         <v>307</v>
       </c>
@@ -26616,7 +26616,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15">
       <c r="A309" s="5">
         <v>308</v>
       </c>
@@ -26654,7 +26654,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15">
       <c r="A310" s="5">
         <v>309</v>
       </c>
@@ -26692,7 +26692,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15">
       <c r="A311" s="5">
         <v>310</v>
       </c>
@@ -26730,7 +26730,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15">
       <c r="A312" s="5">
         <v>311</v>
       </c>
@@ -26768,7 +26768,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15">
       <c r="A313" s="5">
         <v>312</v>
       </c>
@@ -26806,7 +26806,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15">
       <c r="A314" s="5">
         <v>313</v>
       </c>
@@ -26844,7 +26844,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15">
       <c r="A315" s="5">
         <v>314</v>
       </c>
@@ -26882,7 +26882,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15">
       <c r="A316" s="5">
         <v>315</v>
       </c>
@@ -26920,7 +26920,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15">
       <c r="A317" s="5">
         <v>316</v>
       </c>
@@ -26961,7 +26961,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15">
       <c r="A318" s="5">
         <v>317</v>
       </c>
@@ -27002,7 +27002,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15">
       <c r="A319" s="5">
         <v>318</v>
       </c>
@@ -27043,7 +27043,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15">
       <c r="A320" s="5">
         <v>319</v>
       </c>
@@ -27084,7 +27084,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15">
       <c r="A321" s="5">
         <v>320</v>
       </c>
@@ -27125,7 +27125,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15">
       <c r="A322" s="5">
         <v>321</v>
       </c>
@@ -27166,7 +27166,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15">
       <c r="A323" s="5">
         <v>322</v>
       </c>
@@ -27207,7 +27207,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15">
       <c r="A324" s="5">
         <v>323</v>
       </c>
@@ -27248,7 +27248,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15">
       <c r="A325" s="5">
         <v>324</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15">
       <c r="A326" s="5">
         <v>325</v>
       </c>
@@ -27330,7 +27330,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15">
       <c r="A327" s="5">
         <v>326</v>
       </c>
@@ -27371,7 +27371,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15">
       <c r="A328" s="5">
         <v>327</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15">
       <c r="A329" s="5">
         <v>328</v>
       </c>
@@ -27453,7 +27453,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15">
       <c r="A330" s="5">
         <v>329</v>
       </c>
@@ -27494,7 +27494,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15">
       <c r="A331" s="5">
         <v>330</v>
       </c>
@@ -27535,7 +27535,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15">
       <c r="A332" s="5">
         <v>331</v>
       </c>
@@ -27573,7 +27573,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15">
       <c r="A333" s="5">
         <v>332</v>
       </c>
@@ -27611,7 +27611,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15">
       <c r="A334" s="5">
         <v>333</v>
       </c>
@@ -27649,7 +27649,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15">
       <c r="A335" s="5">
         <v>334</v>
       </c>
@@ -27687,7 +27687,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15">
       <c r="A336" s="5">
         <v>335</v>
       </c>
@@ -27725,7 +27725,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15">
       <c r="A337" s="5">
         <v>336</v>
       </c>
@@ -27763,7 +27763,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15">
       <c r="A338" s="5">
         <v>337</v>
       </c>
@@ -27801,7 +27801,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15">
       <c r="A339" s="5">
         <v>338</v>
       </c>
@@ -27839,7 +27839,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15">
       <c r="A340" s="5">
         <v>339</v>
       </c>
@@ -27880,7 +27880,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15">
       <c r="A341" s="5">
         <v>340</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15">
       <c r="A342" s="5">
         <v>341</v>
       </c>
@@ -27965,7 +27965,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15">
       <c r="A343" s="5">
         <v>342</v>
       </c>
@@ -28006,7 +28006,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15">
       <c r="A344" s="5">
         <v>343</v>
       </c>
@@ -28047,7 +28047,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15">
       <c r="A345" s="5">
         <v>344</v>
       </c>
@@ -28088,7 +28088,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15">
       <c r="A346" s="5">
         <v>345</v>
       </c>
@@ -28129,7 +28129,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15">
       <c r="A347" s="5">
         <v>346</v>
       </c>
@@ -28170,7 +28170,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15">
       <c r="A348" s="5">
         <v>347</v>
       </c>
@@ -28211,7 +28211,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15">
       <c r="A349" s="5">
         <v>348</v>
       </c>
@@ -28252,7 +28252,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15">
       <c r="A350" s="5">
         <v>349</v>
       </c>
@@ -28293,7 +28293,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15">
       <c r="A351" s="5">
         <v>350</v>
       </c>
@@ -28334,7 +28334,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15">
       <c r="A352" s="5">
         <v>351</v>
       </c>
@@ -28369,7 +28369,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15">
       <c r="A353" s="5">
         <v>352</v>
       </c>
@@ -28410,7 +28410,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15">
       <c r="A354" s="5">
         <v>353</v>
       </c>
@@ -28451,7 +28451,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15">
       <c r="A355" s="5">
         <v>354</v>
       </c>
@@ -28492,7 +28492,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15">
       <c r="A356" s="5">
         <v>355</v>
       </c>
@@ -28533,7 +28533,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15">
       <c r="A357" s="5">
         <v>356</v>
       </c>
@@ -28568,7 +28568,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15">
       <c r="A358" s="5">
         <v>357</v>
       </c>
@@ -28603,7 +28603,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15">
       <c r="A359" s="5">
         <v>358</v>
       </c>
@@ -28638,7 +28638,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15">
       <c r="A360" s="5">
         <v>359</v>
       </c>
@@ -28673,7 +28673,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="361" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:15" ht="17">
       <c r="A361" s="5">
         <v>360</v>
       </c>
@@ -28717,7 +28717,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="362" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:15" ht="17">
       <c r="A362" s="5">
         <v>361</v>
       </c>
@@ -28761,7 +28761,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="363" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:15" ht="17">
       <c r="A363" s="5">
         <v>362</v>
       </c>
@@ -28805,7 +28805,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="364" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:15" ht="17">
       <c r="A364" s="5">
         <v>363</v>
       </c>
@@ -28849,7 +28849,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="365" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:15" ht="17">
       <c r="A365" s="5">
         <v>364</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="366" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:15" ht="17">
       <c r="A366" s="5">
         <v>365</v>
       </c>
@@ -28937,7 +28937,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="367" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:15" ht="17">
       <c r="A367" s="5">
         <v>366</v>
       </c>
@@ -28981,7 +28981,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="368" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:15" ht="17">
       <c r="A368" s="5">
         <v>367</v>
       </c>
@@ -29025,7 +29025,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:15" ht="17">
       <c r="A369" s="5">
         <v>368</v>
       </c>
@@ -29069,7 +29069,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:15" ht="17">
       <c r="A370" s="5">
         <v>369</v>
       </c>
@@ -29113,7 +29113,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:15" ht="17">
       <c r="A371" s="5">
         <v>370</v>
       </c>
@@ -29157,7 +29157,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="372" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:15" ht="17">
       <c r="A372" s="5">
         <v>371</v>
       </c>
@@ -29201,7 +29201,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="373" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:15" ht="17">
       <c r="A373" s="5">
         <v>372</v>
       </c>
@@ -29245,7 +29245,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15">
       <c r="A374" s="5">
         <v>373</v>
       </c>
@@ -29289,7 +29289,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15">
       <c r="A375" s="5">
         <v>374</v>
       </c>
@@ -29333,7 +29333,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15">
       <c r="A376" s="5">
         <v>375</v>
       </c>
@@ -29377,7 +29377,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15">
       <c r="A377" s="5">
         <v>376</v>
       </c>
@@ -29421,7 +29421,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15">
       <c r="A378" s="5">
         <v>377</v>
       </c>
@@ -29465,7 +29465,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15">
       <c r="A379" s="5">
         <v>378</v>
       </c>
@@ -29509,7 +29509,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15">
       <c r="A380" s="5">
         <v>379</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15">
       <c r="A381" s="5">
         <v>380</v>
       </c>
@@ -29594,7 +29594,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15">
       <c r="A382" s="5">
         <v>381</v>
       </c>
@@ -29638,7 +29638,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15">
       <c r="A383" s="5">
         <v>382</v>
       </c>
@@ -29682,7 +29682,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15">
       <c r="A384" s="5">
         <v>383</v>
       </c>
@@ -29726,7 +29726,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15">
       <c r="A385" s="5">
         <v>384</v>
       </c>
@@ -29770,7 +29770,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15">
       <c r="A386" s="5">
         <v>385</v>
       </c>
@@ -29814,7 +29814,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15">
       <c r="A387" s="5">
         <v>386</v>
       </c>
@@ -29858,7 +29858,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15">
       <c r="A388" s="5">
         <v>387</v>
       </c>
@@ -29902,7 +29902,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15">
       <c r="A389" s="5">
         <v>388</v>
       </c>
@@ -29946,7 +29946,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15">
       <c r="A390" s="5">
         <v>389</v>
       </c>
@@ -29990,7 +29990,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15">
       <c r="A391" s="5">
         <v>390</v>
       </c>
@@ -30034,7 +30034,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15">
       <c r="A392" s="5">
         <v>391</v>
       </c>
@@ -30078,7 +30078,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15">
       <c r="A393" s="5">
         <v>392</v>
       </c>
@@ -30122,7 +30122,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15">
       <c r="A394" s="5">
         <v>393</v>
       </c>
@@ -30166,7 +30166,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15">
       <c r="A395" s="5">
         <v>394</v>
       </c>
@@ -30210,7 +30210,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15">
       <c r="A396" s="5">
         <v>395</v>
       </c>
@@ -30254,7 +30254,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15">
       <c r="A397" s="5">
         <v>396</v>
       </c>
@@ -30295,7 +30295,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15">
       <c r="A398" s="5">
         <v>397</v>
       </c>
@@ -30336,7 +30336,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15">
       <c r="A399" s="5">
         <v>398</v>
       </c>
@@ -30377,7 +30377,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15">
       <c r="A400" s="5">
         <v>399</v>
       </c>
@@ -30418,7 +30418,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14">
       <c r="A401" s="5">
         <v>400</v>
       </c>
@@ -30459,7 +30459,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14">
       <c r="A402" s="5">
         <v>401</v>
       </c>
@@ -30500,7 +30500,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14">
       <c r="A403" s="5">
         <v>402</v>
       </c>
@@ -30541,7 +30541,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:14">
       <c r="A404" s="5">
         <v>403</v>
       </c>
@@ -30582,7 +30582,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:14">
       <c r="A405" s="5">
         <v>404</v>
       </c>
@@ -30623,7 +30623,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:14">
       <c r="A406" s="5">
         <v>405</v>
       </c>
@@ -30664,7 +30664,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:14">
       <c r="A407" s="5">
         <v>406</v>
       </c>
@@ -30705,7 +30705,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:14">
       <c r="A408" s="5">
         <v>407</v>
       </c>
@@ -30746,7 +30746,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:14">
       <c r="A409" s="5">
         <v>408</v>
       </c>
@@ -30787,7 +30787,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:14">
       <c r="A410" s="5">
         <v>409</v>
       </c>
@@ -30828,7 +30828,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:14">
       <c r="A411" s="5">
         <v>410</v>
       </c>
@@ -30869,7 +30869,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:14">
       <c r="A412" s="5">
         <v>411</v>
       </c>
@@ -30910,7 +30910,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:14">
       <c r="A413" s="5">
         <v>412</v>
       </c>
@@ -30951,7 +30951,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:14">
       <c r="A414" s="5">
         <v>413</v>
       </c>
@@ -30992,7 +30992,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:14">
       <c r="A415" s="5">
         <v>414</v>
       </c>
@@ -31033,7 +31033,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:14">
       <c r="A416" s="5">
         <v>415</v>
       </c>
@@ -31074,7 +31074,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14">
       <c r="A417" s="5">
         <v>416</v>
       </c>
@@ -31115,7 +31115,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:14">
       <c r="A418" s="5">
         <v>417</v>
       </c>
@@ -31156,7 +31156,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14">
       <c r="A419" s="5">
         <v>418</v>
       </c>
@@ -31197,7 +31197,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:14">
       <c r="A420" s="5">
         <v>419</v>
       </c>
@@ -31238,7 +31238,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:14">
       <c r="A421" s="5">
         <v>420</v>
       </c>
@@ -31279,7 +31279,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:14">
       <c r="A422" s="5">
         <v>421</v>
       </c>
@@ -31320,7 +31320,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14">
       <c r="A423" s="5">
         <v>422</v>
       </c>
@@ -31361,7 +31361,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:14">
       <c r="A424" s="5">
         <v>423</v>
       </c>
@@ -31402,7 +31402,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:14">
       <c r="A425" s="5">
         <v>424</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:14">
       <c r="A426" s="5">
         <v>425</v>
       </c>
@@ -31484,7 +31484,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:14">
       <c r="A427" s="5">
         <v>426</v>
       </c>
@@ -31525,7 +31525,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:14">
       <c r="A428" s="5">
         <v>427</v>
       </c>
@@ -31566,7 +31566,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:14">
       <c r="A429" s="5">
         <v>428</v>
       </c>
@@ -31607,7 +31607,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:14">
       <c r="A430" s="5">
         <v>429</v>
       </c>
@@ -31648,7 +31648,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:14">
       <c r="A431" s="5">
         <v>430</v>
       </c>
@@ -31689,7 +31689,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:14">
       <c r="A432" s="5">
         <v>431</v>
       </c>
@@ -31730,7 +31730,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:14">
       <c r="A433" s="5">
         <v>432</v>
       </c>
@@ -31771,7 +31771,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:14">
       <c r="A434" s="5">
         <v>433</v>
       </c>
@@ -31812,7 +31812,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:14">
       <c r="A435" s="5">
         <v>434</v>
       </c>
@@ -31853,7 +31853,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:14">
       <c r="A436" s="5">
         <v>435</v>
       </c>
@@ -31894,7 +31894,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14">
       <c r="A437" s="5">
         <v>436</v>
       </c>
@@ -31935,7 +31935,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:14">
       <c r="A438" s="5">
         <v>437</v>
       </c>
@@ -31976,7 +31976,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:14">
       <c r="A439" s="5">
         <v>438</v>
       </c>
@@ -32017,7 +32017,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:14">
       <c r="A440" s="5">
         <v>439</v>
       </c>
@@ -32058,7 +32058,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:14">
       <c r="A441" s="5">
         <v>440</v>
       </c>
@@ -32099,7 +32099,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:14">
       <c r="A442" s="5">
         <v>441</v>
       </c>
@@ -32140,7 +32140,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:14">
       <c r="A443" s="5">
         <v>442</v>
       </c>
@@ -32181,7 +32181,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:14">
       <c r="A444" s="5">
         <v>443</v>
       </c>
@@ -32222,7 +32222,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:14">
       <c r="A445" s="5">
         <v>444</v>
       </c>
@@ -32263,7 +32263,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:14">
       <c r="A446" s="5">
         <v>445</v>
       </c>
@@ -32304,7 +32304,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:14">
       <c r="A447" s="5">
         <v>446</v>
       </c>
@@ -32345,7 +32345,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:14">
       <c r="A448" s="5">
         <v>447</v>
       </c>
@@ -32386,7 +32386,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15">
       <c r="A449" s="5">
         <v>448</v>
       </c>
@@ -32427,7 +32427,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15">
       <c r="A450" s="5">
         <v>449</v>
       </c>
@@ -32468,7 +32468,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15">
       <c r="A451" s="5">
         <v>450</v>
       </c>
@@ -32509,7 +32509,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15">
       <c r="A452" s="5">
         <v>451</v>
       </c>
@@ -32553,7 +32553,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15">
       <c r="A453" s="5">
         <v>452</v>
       </c>
@@ -32597,7 +32597,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15">
       <c r="A454" s="5">
         <v>453</v>
       </c>
@@ -32641,7 +32641,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15">
       <c r="A455" s="5">
         <v>454</v>
       </c>
@@ -32685,7 +32685,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15">
       <c r="A456" s="5">
         <v>455</v>
       </c>
@@ -32729,7 +32729,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15">
       <c r="A457" s="5">
         <v>456</v>
       </c>
@@ -32773,7 +32773,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15">
       <c r="A458" s="5">
         <v>457</v>
       </c>
@@ -32817,7 +32817,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15">
       <c r="A459" s="5">
         <v>458</v>
       </c>
@@ -32861,7 +32861,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15">
       <c r="A460" s="5">
         <v>459</v>
       </c>
@@ -32905,7 +32905,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15">
       <c r="A461" s="5">
         <v>460</v>
       </c>
@@ -32949,7 +32949,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15">
       <c r="A462" s="5">
         <v>461</v>
       </c>
@@ -32993,7 +32993,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15">
       <c r="A463" s="5">
         <v>462</v>
       </c>
@@ -33037,7 +33037,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15">
       <c r="A464" s="5">
         <v>463</v>
       </c>
@@ -33081,7 +33081,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15">
       <c r="A465" s="5">
         <v>464</v>
       </c>
@@ -33125,7 +33125,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15">
       <c r="A466" s="5">
         <v>465</v>
       </c>
@@ -33169,7 +33169,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15">
       <c r="A467" s="5">
         <v>466</v>
       </c>
@@ -33213,7 +33213,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15">
       <c r="A468" s="5">
         <v>467</v>
       </c>
@@ -33257,7 +33257,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15">
       <c r="A469" s="5">
         <v>468</v>
       </c>
@@ -33301,7 +33301,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15">
       <c r="A470" s="5">
         <v>469</v>
       </c>
@@ -33345,7 +33345,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15">
       <c r="A471" s="5">
         <v>470</v>
       </c>
@@ -33389,7 +33389,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15">
       <c r="A472" s="5">
         <v>471</v>
       </c>
@@ -33433,7 +33433,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15">
       <c r="A473" s="5">
         <v>472</v>
       </c>
@@ -33477,7 +33477,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15">
       <c r="A474" s="5">
         <v>473</v>
       </c>
@@ -33521,7 +33521,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15">
       <c r="A475" s="5">
         <v>474</v>
       </c>
@@ -33565,7 +33565,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15">
       <c r="A476" s="5">
         <v>475</v>
       </c>
@@ -33609,7 +33609,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15">
       <c r="A477" s="5">
         <v>476</v>
       </c>
@@ -33653,7 +33653,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15">
       <c r="A478" s="5">
         <v>477</v>
       </c>
@@ -33697,7 +33697,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15">
       <c r="A479" s="5">
         <v>478</v>
       </c>
@@ -33741,7 +33741,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15">
       <c r="A480" s="5">
         <v>479</v>
       </c>
@@ -33785,7 +33785,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15">
       <c r="A481" s="5">
         <v>480</v>
       </c>
@@ -33829,7 +33829,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15">
       <c r="A482" s="5">
         <v>481</v>
       </c>
@@ -33873,7 +33873,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15">
       <c r="A483" s="5">
         <v>482</v>
       </c>
@@ -33917,7 +33917,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15">
       <c r="A484" s="5">
         <v>483</v>
       </c>
@@ -33961,7 +33961,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15">
       <c r="A485" s="5">
         <v>484</v>
       </c>
@@ -34005,7 +34005,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15">
       <c r="A486" s="5">
         <v>485</v>
       </c>
@@ -34049,7 +34049,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15">
       <c r="A487" s="5">
         <v>486</v>
       </c>
@@ -34093,7 +34093,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15">
       <c r="A488" s="5">
         <v>487</v>
       </c>
@@ -34137,7 +34137,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="489" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:15" ht="17">
       <c r="A489" s="5">
         <v>488</v>
       </c>
@@ -34181,7 +34181,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="490" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:15" ht="17">
       <c r="A490" s="5">
         <v>489</v>
       </c>
@@ -34225,7 +34225,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="491" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:15" ht="17">
       <c r="A491" s="5">
         <v>490</v>
       </c>
@@ -34269,7 +34269,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15">
       <c r="A492" s="5">
         <v>491</v>
       </c>
@@ -34313,7 +34313,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15">
       <c r="A493" s="5">
         <v>492</v>
       </c>
@@ -34357,7 +34357,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15">
       <c r="A494" s="5">
         <v>493</v>
       </c>
@@ -34401,7 +34401,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15">
       <c r="A495" s="5">
         <v>494</v>
       </c>
@@ -34445,7 +34445,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="496" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:15" ht="17">
       <c r="A496" s="5">
         <v>495</v>
       </c>
@@ -34486,7 +34486,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="497" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:14" ht="17">
       <c r="A497" s="5">
         <v>496</v>
       </c>
@@ -34527,7 +34527,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:14">
       <c r="A498" s="5">
         <v>497</v>
       </c>
@@ -34565,7 +34565,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:14">
       <c r="A499" s="5">
         <v>498</v>
       </c>
@@ -34603,7 +34603,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:14">
       <c r="A500" s="5">
         <v>499</v>
       </c>
@@ -34641,7 +34641,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:14">
       <c r="A501" s="5">
         <v>500</v>
       </c>
@@ -34679,7 +34679,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:14">
       <c r="A502" s="5">
         <v>501</v>
       </c>
@@ -34717,7 +34717,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:14">
       <c r="A503" s="5">
         <v>502</v>
       </c>
@@ -34755,7 +34755,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:14">
       <c r="A504" s="5">
         <v>503</v>
       </c>
@@ -34793,7 +34793,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:14">
       <c r="A505" s="5">
         <v>504</v>
       </c>
@@ -34831,7 +34831,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:14">
       <c r="A506" s="5">
         <v>505</v>
       </c>
@@ -34869,7 +34869,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:14">
       <c r="A507" s="5">
         <v>506</v>
       </c>
@@ -34907,7 +34907,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:14">
       <c r="A508" s="5">
         <v>507</v>
       </c>
@@ -34945,7 +34945,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:14">
       <c r="A509" s="5">
         <v>508</v>
       </c>
@@ -34983,7 +34983,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:14">
       <c r="A510" s="5">
         <v>509</v>
       </c>
@@ -35021,7 +35021,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:14">
       <c r="A511" s="5">
         <v>510</v>
       </c>
@@ -35059,7 +35059,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:14">
       <c r="A512" s="5">
         <v>511</v>
       </c>
@@ -35097,7 +35097,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15">
       <c r="A513" s="5">
         <v>512</v>
       </c>
@@ -35135,7 +35135,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15">
       <c r="A514" s="5">
         <v>513</v>
       </c>
@@ -35173,7 +35173,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15">
       <c r="A515" s="5">
         <v>514</v>
       </c>
@@ -35214,7 +35214,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15">
       <c r="A516" s="5">
         <v>515</v>
       </c>
@@ -35252,7 +35252,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15">
       <c r="A517" s="5">
         <v>516</v>
       </c>
@@ -35290,7 +35290,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15">
       <c r="A518" s="5">
         <v>517</v>
       </c>
@@ -35328,7 +35328,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15">
       <c r="A519" s="5">
         <v>518</v>
       </c>
@@ -35366,7 +35366,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15">
       <c r="A520" s="5">
         <v>519</v>
       </c>
@@ -35404,7 +35404,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15">
       <c r="A521" s="5">
         <v>520</v>
       </c>
@@ -35442,7 +35442,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15">
       <c r="A522" s="5">
         <v>521</v>
       </c>
@@ -35480,7 +35480,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15">
       <c r="A523" s="5">
         <v>522</v>
       </c>
@@ -35518,7 +35518,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15">
       <c r="A524" s="5">
         <v>523</v>
       </c>
@@ -35556,7 +35556,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15">
       <c r="A525" s="5">
         <v>524</v>
       </c>
@@ -35594,7 +35594,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15">
       <c r="A526" s="5">
         <v>525</v>
       </c>
@@ -35632,7 +35632,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15">
       <c r="A527" s="5">
         <v>526</v>
       </c>
@@ -35670,7 +35670,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15">
       <c r="A528" s="5">
         <v>527</v>
       </c>
@@ -35708,7 +35708,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:14">
       <c r="A529" s="5">
         <v>528</v>
       </c>
@@ -35746,7 +35746,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:14">
       <c r="A530" s="5">
         <v>529</v>
       </c>
@@ -35784,7 +35784,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:14">
       <c r="A531" s="5">
         <v>530</v>
       </c>
@@ -35822,7 +35822,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:14">
       <c r="A532" s="5">
         <v>531</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:14">
       <c r="A533" s="5">
         <v>532</v>
       </c>
@@ -35898,7 +35898,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:14">
       <c r="A534" s="5">
         <v>533</v>
       </c>
@@ -35936,7 +35936,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:14">
       <c r="A535" s="5">
         <v>534</v>
       </c>
@@ -35974,7 +35974,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:14">
       <c r="A536" s="5">
         <v>535</v>
       </c>
@@ -36012,7 +36012,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:14">
       <c r="A537" s="5">
         <v>536</v>
       </c>
@@ -36050,7 +36050,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:14">
       <c r="A538" s="5">
         <v>537</v>
       </c>
@@ -36088,7 +36088,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:14">
       <c r="A539" s="5">
         <v>538</v>
       </c>
@@ -36126,7 +36126,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:14">
       <c r="A540" s="5">
         <v>539</v>
       </c>
@@ -36164,7 +36164,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:14">
       <c r="A541" s="5">
         <v>540</v>
       </c>
@@ -36202,7 +36202,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:14">
       <c r="A542" s="5">
         <v>541</v>
       </c>
@@ -36240,7 +36240,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:14">
       <c r="A543" s="5">
         <v>542</v>
       </c>
@@ -36278,7 +36278,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:14">
       <c r="A544" s="5">
         <v>543</v>
       </c>
@@ -36316,7 +36316,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:14">
       <c r="A545" s="5">
         <v>544</v>
       </c>
@@ -36354,7 +36354,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:14">
       <c r="A546" s="5">
         <v>545</v>
       </c>
@@ -36392,7 +36392,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:14">
       <c r="A547" s="5">
         <v>546</v>
       </c>
@@ -36430,7 +36430,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:14">
       <c r="A548" s="5">
         <v>547</v>
       </c>
@@ -36468,7 +36468,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:14">
       <c r="A549" s="5">
         <v>548</v>
       </c>
@@ -36506,7 +36506,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:14">
       <c r="A550" s="5">
         <v>549</v>
       </c>
@@ -36544,7 +36544,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:14">
       <c r="A551" s="5">
         <v>550</v>
       </c>
@@ -36582,7 +36582,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:14">
       <c r="A552" s="5">
         <v>551</v>
       </c>
@@ -36620,7 +36620,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:14">
       <c r="A553" s="5">
         <v>552</v>
       </c>
@@ -36658,7 +36658,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:14">
       <c r="A554" s="5">
         <v>553</v>
       </c>
@@ -36696,7 +36696,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:14">
       <c r="A555" s="5">
         <v>554</v>
       </c>
@@ -36734,7 +36734,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:14">
       <c r="A556" s="5">
         <v>555</v>
       </c>
@@ -36772,7 +36772,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:14">
       <c r="A557" s="5">
         <v>556</v>
       </c>
@@ -36810,7 +36810,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:14">
       <c r="A558" s="5">
         <v>557</v>
       </c>
@@ -36848,7 +36848,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:14">
       <c r="A559" s="5">
         <v>558</v>
       </c>
@@ -36886,7 +36886,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:14">
       <c r="A560" s="5">
         <v>559</v>
       </c>
@@ -36924,7 +36924,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:14">
       <c r="A561" s="5">
         <v>560</v>
       </c>
@@ -36962,7 +36962,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:14">
       <c r="A562" s="5">
         <v>561</v>
       </c>
@@ -37000,7 +37000,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:14">
       <c r="A563" s="5">
         <v>562</v>
       </c>
@@ -37038,7 +37038,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:14">
       <c r="A564" s="5">
         <v>563</v>
       </c>
@@ -37076,7 +37076,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:14">
       <c r="A565" s="5">
         <v>564</v>
       </c>
@@ -37114,7 +37114,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:14">
       <c r="A566" s="5">
         <v>565</v>
       </c>
@@ -37152,7 +37152,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:14">
       <c r="A567" s="5">
         <v>566</v>
       </c>
@@ -37190,7 +37190,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="568" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:14">
       <c r="A568" s="5">
         <v>567</v>
       </c>
@@ -37228,7 +37228,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:14">
       <c r="A569" s="5">
         <v>568</v>
       </c>
@@ -37266,7 +37266,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="570" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:14">
       <c r="A570" s="5">
         <v>569</v>
       </c>
@@ -37304,7 +37304,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:14">
       <c r="A571" s="5">
         <v>570</v>
       </c>
@@ -37342,7 +37342,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:14">
       <c r="A572" s="5">
         <v>571</v>
       </c>
@@ -37380,7 +37380,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="573" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:14">
       <c r="A573" s="5">
         <v>572</v>
       </c>
@@ -37418,7 +37418,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="574" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:14">
       <c r="A574" s="5">
         <v>573</v>
       </c>
@@ -37456,7 +37456,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="575" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:14">
       <c r="A575" s="5">
         <v>574</v>
       </c>
@@ -37494,7 +37494,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="576" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:14">
       <c r="A576" s="5">
         <v>575</v>
       </c>
@@ -37532,7 +37532,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:14">
       <c r="A577" s="5">
         <v>576</v>
       </c>
@@ -37570,7 +37570,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:14">
       <c r="A578" s="5">
         <v>577</v>
       </c>
@@ -37608,7 +37608,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:14">
       <c r="A579" s="5">
         <v>578</v>
       </c>
@@ -37646,7 +37646,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="580" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:14">
       <c r="A580" s="5">
         <v>579</v>
       </c>
@@ -37684,7 +37684,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="581" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:14">
       <c r="A581" s="5">
         <v>580</v>
       </c>
@@ -37722,7 +37722,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:14">
       <c r="A582" s="5">
         <v>581</v>
       </c>
@@ -37760,7 +37760,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:14">
       <c r="A583" s="5">
         <v>582</v>
       </c>
@@ -37798,7 +37798,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:14">
       <c r="A584" s="5">
         <v>583</v>
       </c>
@@ -37836,7 +37836,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:14">
       <c r="A585" s="5">
         <v>584</v>
       </c>
@@ -37874,7 +37874,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:14">
       <c r="A586" s="5">
         <v>585</v>
       </c>
@@ -37912,7 +37912,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:14">
       <c r="A587" s="5">
         <v>586</v>
       </c>
@@ -37950,7 +37950,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="588" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:14">
       <c r="A588" s="5">
         <v>587</v>
       </c>
@@ -37988,7 +37988,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:14">
       <c r="A589" s="5">
         <v>588</v>
       </c>
@@ -38026,7 +38026,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="590" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:14">
       <c r="A590" s="5">
         <v>589</v>
       </c>
@@ -38064,7 +38064,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:14">
       <c r="A591" s="5">
         <v>590</v>
       </c>
@@ -38102,7 +38102,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:14">
       <c r="A592" s="5">
         <v>591</v>
       </c>
@@ -38140,7 +38140,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="593" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:15" ht="17">
       <c r="A593" s="5">
         <v>592</v>
       </c>
@@ -38184,7 +38184,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="594" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:15" ht="17">
       <c r="A594" s="5">
         <v>593</v>
       </c>
@@ -38228,7 +38228,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="595" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:15" ht="17">
       <c r="A595" s="5">
         <v>594</v>
       </c>
@@ -38272,7 +38272,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="596" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:15" ht="17">
       <c r="A596" s="5">
         <v>595</v>
       </c>
@@ -38316,7 +38316,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="597" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:15" ht="17">
       <c r="A597" s="5">
         <v>596</v>
       </c>
@@ -38360,7 +38360,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="598" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:15" ht="17">
       <c r="A598" s="5">
         <v>597</v>
       </c>
@@ -38404,7 +38404,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="599" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:15" ht="17">
       <c r="A599" s="5">
         <v>598</v>
       </c>
@@ -38448,7 +38448,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="600" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:15" ht="17">
       <c r="A600" s="5">
         <v>599</v>
       </c>
@@ -38492,7 +38492,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="601" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:15" ht="17">
       <c r="A601" s="5">
         <v>600</v>
       </c>
@@ -38536,7 +38536,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="602" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:15" ht="17">
       <c r="A602" s="5">
         <v>601</v>
       </c>
@@ -38577,7 +38577,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="603" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:15" ht="17">
       <c r="A603" s="5">
         <v>602</v>
       </c>
@@ -38621,7 +38621,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="604" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:15" ht="17">
       <c r="A604" s="5">
         <v>603</v>
       </c>
@@ -38665,7 +38665,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="605" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:15" ht="17">
       <c r="A605" s="5">
         <v>604</v>
       </c>
@@ -38709,7 +38709,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="606" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:15" ht="17">
       <c r="A606" s="5">
         <v>605</v>
       </c>
@@ -38753,7 +38753,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="607" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:15" ht="17">
       <c r="A607" s="5">
         <v>606</v>
       </c>
@@ -38797,7 +38797,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="608" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:15" ht="17">
       <c r="A608" s="5">
         <v>607</v>
       </c>
@@ -38841,7 +38841,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="609" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:15" ht="17">
       <c r="A609" s="5">
         <v>608</v>
       </c>
@@ -38885,7 +38885,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="610" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:15" ht="17">
       <c r="A610" s="5">
         <v>609</v>
       </c>
@@ -38929,7 +38929,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15">
       <c r="A611" s="5">
         <v>610</v>
       </c>
@@ -38970,7 +38970,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15">
       <c r="A612" s="5">
         <v>611</v>
       </c>
@@ -39011,7 +39011,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15">
       <c r="A613" s="5">
         <v>612</v>
       </c>
@@ -39052,7 +39052,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15">
       <c r="A614" s="5">
         <v>613</v>
       </c>
@@ -39090,7 +39090,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15">
       <c r="A615" s="5">
         <v>614</v>
       </c>
@@ -39131,7 +39131,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15">
       <c r="A616" s="5">
         <v>615</v>
       </c>
@@ -39175,7 +39175,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15">
       <c r="A617" s="5">
         <v>616</v>
       </c>
@@ -39219,7 +39219,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15">
       <c r="A618" s="5">
         <v>617</v>
       </c>
@@ -39263,7 +39263,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15">
       <c r="A619" s="5">
         <v>618</v>
       </c>
@@ -39301,7 +39301,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15">
       <c r="A620" s="5">
         <v>619</v>
       </c>
@@ -39342,7 +39342,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15">
       <c r="A621" s="5">
         <v>620</v>
       </c>
@@ -39383,7 +39383,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15">
       <c r="A622" s="5">
         <v>621</v>
       </c>
@@ -39424,7 +39424,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15">
       <c r="A623" s="5">
         <v>622</v>
       </c>
@@ -39468,7 +39468,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15">
       <c r="A624" s="5">
         <v>623</v>
       </c>
@@ -39512,7 +39512,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15">
       <c r="A625" s="5">
         <v>624</v>
       </c>
@@ -39556,7 +39556,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15">
       <c r="A626" s="5">
         <v>625</v>
       </c>
@@ -39600,7 +39600,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15">
       <c r="A627" s="5">
         <v>626</v>
       </c>
@@ -39644,7 +39644,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15">
       <c r="A628" s="5">
         <v>627</v>
       </c>
@@ -39685,7 +39685,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15">
       <c r="A629" s="5">
         <v>628</v>
       </c>
@@ -39729,7 +39729,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15">
       <c r="A630" s="5">
         <v>629</v>
       </c>
@@ -39770,7 +39770,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15">
       <c r="A631" s="5">
         <v>630</v>
       </c>
@@ -39811,7 +39811,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:15">
       <c r="A632" s="5">
         <v>631</v>
       </c>
@@ -39852,7 +39852,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15">
       <c r="A633" s="5">
         <v>632</v>
       </c>
@@ -39890,7 +39890,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15">
       <c r="A634" s="5">
         <v>633</v>
       </c>
@@ -39931,7 +39931,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15">
       <c r="A635" s="5">
         <v>634</v>
       </c>
@@ -39972,7 +39972,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:15">
       <c r="A636" s="5">
         <v>635</v>
       </c>
@@ -40013,7 +40013,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:15">
       <c r="A637" s="5">
         <v>636</v>
       </c>
@@ -40054,7 +40054,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:15">
       <c r="A638" s="5">
         <v>637</v>
       </c>
@@ -40095,7 +40095,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15">
       <c r="A639" s="5">
         <v>638</v>
       </c>
@@ -40136,7 +40136,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15">
       <c r="A640" s="5">
         <v>639</v>
       </c>
@@ -40177,7 +40177,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15">
       <c r="A641" s="5">
         <v>640</v>
       </c>
@@ -40218,7 +40218,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15">
       <c r="A642" s="5">
         <v>641</v>
       </c>
@@ -40262,7 +40262,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15">
       <c r="A643" s="5">
         <v>642</v>
       </c>
@@ -40303,7 +40303,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15">
       <c r="A644" s="5">
         <v>643</v>
       </c>
@@ -40344,7 +40344,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15">
       <c r="A645" s="5">
         <v>644</v>
       </c>
@@ -40385,7 +40385,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15">
       <c r="A646" s="5">
         <v>645</v>
       </c>
@@ -40426,7 +40426,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15">
       <c r="A647" s="5">
         <v>646</v>
       </c>
@@ -40467,7 +40467,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15">
       <c r="A648" s="5">
         <v>647</v>
       </c>
@@ -40508,7 +40508,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15">
       <c r="A649" s="5">
         <v>648</v>
       </c>
@@ -40549,7 +40549,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15">
       <c r="A650" s="5">
         <v>649</v>
       </c>
@@ -40590,7 +40590,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="651" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:15" ht="17">
       <c r="A651" s="5">
         <v>650</v>
       </c>
@@ -40631,7 +40631,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:15" ht="17">
       <c r="A652" s="5">
         <v>651</v>
       </c>
@@ -40672,7 +40672,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:15" ht="17">
       <c r="A653" s="5">
         <v>652</v>
       </c>
@@ -40713,7 +40713,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:15" ht="17">
       <c r="A654" s="5">
         <v>653</v>
       </c>
@@ -40754,7 +40754,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:15" ht="17">
       <c r="A655" s="5">
         <v>654</v>
       </c>
@@ -40795,7 +40795,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:15" ht="17">
       <c r="A656" s="5">
         <v>655</v>
       </c>
@@ -40836,7 +40836,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="657" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:14" ht="17">
       <c r="A657" s="5">
         <v>656</v>
       </c>
@@ -40877,7 +40877,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="658" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:14" ht="17">
       <c r="A658" s="5">
         <v>657</v>
       </c>
@@ -40918,7 +40918,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="659" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:14" ht="17">
       <c r="A659" s="5">
         <v>658</v>
       </c>
@@ -40959,7 +40959,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="660" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:14" ht="17">
       <c r="A660" s="5">
         <v>659</v>
       </c>
@@ -41000,7 +41000,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="661" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:14" ht="17">
       <c r="A661" s="5">
         <v>660</v>
       </c>
@@ -41041,7 +41041,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="662" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:14" ht="17">
       <c r="A662" s="5">
         <v>661</v>
       </c>
@@ -41082,7 +41082,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="663" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:14" ht="17">
       <c r="A663" s="5">
         <v>662</v>
       </c>
@@ -41123,7 +41123,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="664" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:14" ht="17">
       <c r="A664" s="5">
         <v>663</v>
       </c>
@@ -41164,7 +41164,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="665" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:14" ht="17">
       <c r="A665" s="5">
         <v>664</v>
       </c>
@@ -41205,7 +41205,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="666" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:14" ht="17">
       <c r="A666" s="5">
         <v>665</v>
       </c>
@@ -41246,7 +41246,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="667" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:14">
       <c r="A667" s="5">
         <v>666</v>
       </c>
@@ -41278,7 +41278,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="668" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:14">
       <c r="A668" s="5">
         <v>667</v>
       </c>
@@ -41310,7 +41310,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="669" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:14">
       <c r="A669" s="5">
         <v>668</v>
       </c>
@@ -41342,7 +41342,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="670" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:14">
       <c r="A670" s="5">
         <v>669</v>
       </c>
@@ -41374,7 +41374,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="671" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:14" ht="17">
       <c r="A671" s="5">
         <v>670</v>
       </c>
@@ -41415,7 +41415,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="672" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:14" ht="17">
       <c r="A672" s="5">
         <v>671</v>
       </c>
@@ -41456,7 +41456,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="673" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:15" ht="17">
       <c r="A673" s="5">
         <v>672</v>
       </c>
@@ -41497,7 +41497,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:15" ht="17">
       <c r="A674" s="5">
         <v>673</v>
       </c>
@@ -41538,7 +41538,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="675" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:15" ht="17">
       <c r="A675" s="5">
         <v>674</v>
       </c>
@@ -41579,7 +41579,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="676" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:15" ht="17">
       <c r="A676" s="5">
         <v>675</v>
       </c>
@@ -41623,7 +41623,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:15" ht="17">
       <c r="A677" s="5">
         <v>676</v>
       </c>
@@ -41667,7 +41667,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:15" ht="17">
       <c r="A678" s="5">
         <v>677</v>
       </c>
@@ -41708,7 +41708,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="679" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:15" ht="17">
       <c r="A679" s="5">
         <v>678</v>
       </c>
@@ -41749,7 +41749,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="680" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:15" ht="17">
       <c r="A680" s="5">
         <v>679</v>
       </c>
@@ -41790,7 +41790,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="681" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:15" ht="17">
       <c r="A681" s="5">
         <v>680</v>
       </c>
@@ -41831,7 +41831,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="682" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:15" ht="17">
       <c r="A682" s="5">
         <v>681</v>
       </c>
@@ -41872,7 +41872,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:15" ht="17">
       <c r="A683" s="5">
         <v>682</v>
       </c>
@@ -41913,7 +41913,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="684" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:15" ht="17">
       <c r="A684" s="5">
         <v>683</v>
       </c>
@@ -41954,7 +41954,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="685" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:15" ht="17">
       <c r="A685" s="5">
         <v>684</v>
       </c>
@@ -41995,7 +41995,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="686" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:15" ht="17">
       <c r="A686" s="5">
         <v>685</v>
       </c>
@@ -42036,7 +42036,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="687" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:15" ht="17">
       <c r="A687" s="5">
         <v>686</v>
       </c>
@@ -42077,7 +42077,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:15" ht="17">
       <c r="A688" s="5">
         <v>687</v>
       </c>
@@ -42118,7 +42118,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:15" ht="17">
       <c r="A689" s="5">
         <v>688</v>
       </c>
@@ -42159,7 +42159,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:15" ht="17">
       <c r="A690" s="5">
         <v>689</v>
       </c>
@@ -42200,7 +42200,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:15" ht="17">
       <c r="A691" s="5">
         <v>690</v>
       </c>
@@ -42241,7 +42241,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="692" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:15" ht="17">
       <c r="A692" s="5">
         <v>691</v>
       </c>
@@ -42282,7 +42282,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="693" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:15" ht="17">
       <c r="A693" s="5">
         <v>692</v>
       </c>
@@ -42323,7 +42323,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="694" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:15" ht="17">
       <c r="A694" s="5">
         <v>693</v>
       </c>
@@ -42364,7 +42364,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="695" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:15" ht="17">
       <c r="A695" s="5">
         <v>694</v>
       </c>
@@ -42405,7 +42405,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:15" ht="17">
       <c r="A696" s="5">
         <v>695</v>
       </c>
@@ -42449,7 +42449,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:15" ht="17">
       <c r="A697" s="5">
         <v>696</v>
       </c>
@@ -42493,7 +42493,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="698" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:15" ht="17">
       <c r="A698" s="5">
         <v>697</v>
       </c>
@@ -42537,7 +42537,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="699" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:15" ht="17">
       <c r="A699" s="5">
         <v>698</v>
       </c>
@@ -42581,7 +42581,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:15" ht="17">
       <c r="A700" s="5">
         <v>699</v>
       </c>
@@ -42625,7 +42625,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="701" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:15" ht="17">
       <c r="A701" s="5">
         <v>700</v>
       </c>
@@ -42669,7 +42669,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="702" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:15" ht="17">
       <c r="A702" s="5">
         <v>701</v>
       </c>
@@ -42713,7 +42713,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="703" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:15" ht="17">
       <c r="A703" s="5">
         <v>702</v>
       </c>
@@ -42757,7 +42757,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:15" ht="17">
       <c r="A704" s="5">
         <v>703</v>
       </c>
@@ -42798,7 +42798,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="705" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:15" ht="17">
       <c r="A705" s="5">
         <v>704</v>
       </c>
@@ -42842,7 +42842,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="706" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:15" ht="17">
       <c r="A706" s="5">
         <v>705</v>
       </c>
@@ -42883,7 +42883,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:15" ht="17">
       <c r="A707" s="5">
         <v>706</v>
       </c>
@@ -42927,7 +42927,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="708" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:15" ht="17">
       <c r="A708" s="5">
         <v>707</v>
       </c>
@@ -42971,7 +42971,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="709" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:15" ht="17">
       <c r="A709" s="5">
         <v>708</v>
       </c>
@@ -43015,7 +43015,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="710" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:15" ht="17">
       <c r="A710" s="5">
         <v>709</v>
       </c>
@@ -43062,7 +43062,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:15" ht="17">
       <c r="A711" s="5">
         <v>710</v>
       </c>
@@ -43106,7 +43106,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:15" ht="17">
       <c r="A712" s="5">
         <v>711</v>
       </c>
@@ -43150,7 +43150,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:15">
       <c r="A713" s="5">
         <v>712</v>
       </c>
@@ -43191,7 +43191,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:15">
       <c r="A714" s="5">
         <v>713</v>
       </c>
@@ -43232,7 +43232,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:15">
       <c r="A715" s="5">
         <v>714</v>
       </c>
@@ -43273,7 +43273,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:15">
       <c r="A716" s="5">
         <v>715</v>
       </c>
@@ -43314,7 +43314,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:15">
       <c r="A717" s="5">
         <v>716</v>
       </c>
@@ -43355,7 +43355,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:15">
       <c r="A718" s="5">
         <v>717</v>
       </c>
@@ -43396,7 +43396,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="719" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:15" ht="17">
       <c r="A719" s="5">
         <v>718</v>
       </c>
@@ -43437,7 +43437,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="720" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:15" ht="17">
       <c r="A720" s="5">
         <v>719</v>
       </c>
@@ -43478,7 +43478,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="721" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:14" ht="17">
       <c r="A721" s="5">
         <v>720</v>
       </c>
@@ -43519,7 +43519,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="722" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:14" ht="17">
       <c r="A722" s="5">
         <v>721</v>
       </c>
@@ -43560,7 +43560,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="723" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:14" ht="17">
       <c r="A723" s="5">
         <v>722</v>
       </c>
@@ -43601,7 +43601,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="724" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:14" ht="17">
       <c r="A724" s="5">
         <v>723</v>
       </c>
@@ -43642,7 +43642,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="725" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:14" ht="17">
       <c r="A725" s="5">
         <v>724</v>
       </c>
@@ -43683,7 +43683,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="726" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:14" ht="17">
       <c r="A726" s="5">
         <v>725</v>
       </c>
@@ -43724,7 +43724,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="727" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:14" ht="17">
       <c r="A727" s="5">
         <v>726</v>
       </c>
@@ -43765,7 +43765,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="728" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:14" ht="17">
       <c r="A728" s="5">
         <v>727</v>
       </c>
@@ -43806,7 +43806,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="729" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:14" ht="17">
       <c r="A729" s="5">
         <v>728</v>
       </c>
@@ -43847,7 +43847,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="730" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:14" ht="17">
       <c r="A730" s="5">
         <v>729</v>
       </c>
@@ -43888,7 +43888,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="731" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:14" ht="17">
       <c r="A731" s="5">
         <v>730</v>
       </c>
@@ -43929,7 +43929,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="732" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:14" ht="17">
       <c r="A732" s="5">
         <v>731</v>
       </c>
@@ -43970,7 +43970,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="733" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:14" ht="17">
       <c r="A733" s="5">
         <v>732</v>
       </c>
@@ -44011,7 +44011,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="734" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:14" ht="17">
       <c r="A734" s="5">
         <v>733</v>
       </c>
@@ -44052,7 +44052,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="735" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:14" ht="17">
       <c r="A735" s="5">
         <v>734</v>
       </c>
@@ -44093,7 +44093,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="736" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:14" ht="17">
       <c r="A736" s="5">
         <v>735</v>
       </c>
@@ -44134,7 +44134,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="737" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:14" ht="17">
       <c r="A737" s="5">
         <v>736</v>
       </c>
@@ -44175,7 +44175,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="738" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:14" ht="17">
       <c r="A738" s="5">
         <v>737</v>
       </c>
@@ -44216,7 +44216,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="739" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:14" ht="17">
       <c r="A739" s="5">
         <v>738</v>
       </c>
@@ -44257,7 +44257,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="740" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:14" ht="17">
       <c r="A740" s="5">
         <v>739</v>
       </c>
@@ -44298,7 +44298,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="741" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:14" ht="17">
       <c r="A741" s="5">
         <v>740</v>
       </c>
@@ -44339,7 +44339,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="742" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:14" ht="17">
       <c r="A742" s="5">
         <v>741</v>
       </c>
@@ -44380,7 +44380,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="743" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:14" ht="17">
       <c r="A743" s="5">
         <v>742</v>
       </c>
@@ -44421,7 +44421,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="744" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:14" ht="17">
       <c r="A744" s="5">
         <v>743</v>
       </c>
@@ -44462,7 +44462,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="745" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:14" ht="17">
       <c r="A745" s="5">
         <v>744</v>
       </c>
@@ -44503,7 +44503,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="746" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:14" ht="17">
       <c r="A746" s="5">
         <v>745</v>
       </c>
@@ -44544,7 +44544,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="747" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:14" ht="17">
       <c r="A747" s="5">
         <v>746</v>
       </c>
@@ -44585,7 +44585,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="748" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:14" ht="17">
       <c r="A748" s="5">
         <v>747</v>
       </c>
@@ -44626,7 +44626,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="749" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:14" ht="17">
       <c r="A749" s="5">
         <v>748</v>
       </c>
@@ -44667,7 +44667,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="750" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:14" ht="17">
       <c r="A750" s="5">
         <v>749</v>
       </c>
@@ -44708,7 +44708,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="751" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:14" ht="17">
       <c r="A751" s="5">
         <v>750</v>
       </c>
@@ -44749,7 +44749,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="752" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:14" ht="17">
       <c r="A752" s="5">
         <v>751</v>
       </c>
@@ -44790,7 +44790,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="753" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:14" ht="17">
       <c r="A753" s="5">
         <v>752</v>
       </c>
@@ -44831,7 +44831,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="754" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:14" ht="17">
       <c r="A754" s="5">
         <v>753</v>
       </c>
@@ -44872,7 +44872,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="755" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:14" ht="17">
       <c r="A755" s="5">
         <v>754</v>
       </c>
@@ -44913,7 +44913,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="756" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:14" ht="17">
       <c r="A756" s="5">
         <v>755</v>
       </c>
@@ -44954,7 +44954,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="757" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:14" ht="17">
       <c r="A757" s="5">
         <v>756</v>
       </c>
@@ -44995,7 +44995,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="758" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:14" ht="17">
       <c r="A758" s="5">
         <v>757</v>
       </c>
@@ -45036,7 +45036,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="759" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:14" ht="17">
       <c r="A759" s="5">
         <v>758</v>
       </c>
@@ -45077,7 +45077,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="760" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:14" ht="17">
       <c r="A760" s="5">
         <v>759</v>
       </c>
@@ -45118,7 +45118,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="761" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:14" ht="17">
       <c r="A761" s="5">
         <v>760</v>
       </c>
@@ -45159,7 +45159,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="762" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:14" ht="17">
       <c r="A762" s="5">
         <v>761</v>
       </c>
@@ -45203,7 +45203,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="763" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:14" ht="17">
       <c r="A763" s="5">
         <v>762</v>
       </c>
@@ -45247,7 +45247,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="764" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:14" ht="17">
       <c r="A764" s="5">
         <v>763</v>
       </c>
@@ -45291,7 +45291,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="765" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:14" ht="17">
       <c r="A765" s="5">
         <v>764</v>
       </c>
@@ -45335,7 +45335,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="766" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:14" ht="17">
       <c r="A766" s="5">
         <v>765</v>
       </c>
@@ -45379,7 +45379,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="767" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:14" ht="17">
       <c r="A767" s="5">
         <v>766</v>
       </c>
@@ -45423,7 +45423,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="768" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:14" ht="17">
       <c r="A768" s="5">
         <v>767</v>
       </c>
@@ -45467,7 +45467,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="769" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:14" ht="17">
       <c r="A769" s="5">
         <v>768</v>
       </c>
@@ -45511,7 +45511,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="770" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:14" ht="17">
       <c r="A770" s="5">
         <v>769</v>
       </c>
@@ -45555,7 +45555,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="771" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:14" ht="17">
       <c r="A771" s="5">
         <v>770</v>
       </c>
@@ -45599,7 +45599,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="772" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:14" ht="17">
       <c r="A772" s="5">
         <v>771</v>
       </c>
@@ -45643,7 +45643,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="773" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:14" ht="17">
       <c r="A773" s="5">
         <v>772</v>
       </c>
@@ -45687,7 +45687,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="774" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:14" ht="17">
       <c r="A774" s="5">
         <v>773</v>
       </c>
@@ -45731,7 +45731,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="775" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:14" ht="17">
       <c r="A775" s="5">
         <v>774</v>
       </c>
@@ -45775,7 +45775,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="776" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:14" ht="17">
       <c r="A776" s="5">
         <v>775</v>
       </c>
@@ -45819,7 +45819,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="777" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:14" ht="17">
       <c r="A777" s="5">
         <v>776</v>
       </c>
@@ -45863,7 +45863,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="778" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:14" ht="17">
       <c r="A778" s="5">
         <v>777</v>
       </c>
@@ -45907,7 +45907,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="779" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:14" ht="17">
       <c r="A779" s="5">
         <v>778</v>
       </c>
@@ -45948,7 +45948,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="780" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:14" ht="17">
       <c r="A780" s="5">
         <v>779</v>
       </c>
@@ -45989,7 +45989,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="781" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:14" ht="17">
       <c r="A781" s="5">
         <v>780</v>
       </c>
@@ -46030,7 +46030,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="782" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:14" ht="17">
       <c r="A782" s="5">
         <v>781</v>
       </c>
@@ -46071,7 +46071,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="783" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:14" ht="17">
       <c r="A783" s="5">
         <v>782</v>
       </c>
@@ -46112,7 +46112,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="784" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:14" ht="17">
       <c r="A784" s="5">
         <v>783</v>
       </c>
@@ -46153,7 +46153,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="785" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:14" ht="17">
       <c r="A785" s="5">
         <v>784</v>
       </c>
@@ -46194,7 +46194,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="786" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:14" ht="17">
       <c r="A786" s="5">
         <v>785</v>
       </c>
@@ -46235,7 +46235,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="787" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:14" ht="17">
       <c r="A787" s="5">
         <v>786</v>
       </c>
@@ -46276,7 +46276,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="788" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:14" ht="17">
       <c r="A788" s="5">
         <v>787</v>
       </c>
@@ -46317,7 +46317,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="789" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:14" ht="17">
       <c r="A789" s="5">
         <v>788</v>
       </c>
@@ -46358,7 +46358,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="790" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:14" ht="17">
       <c r="A790" s="5">
         <v>789</v>
       </c>
@@ -46399,7 +46399,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="791" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:14" ht="17">
       <c r="A791" s="5">
         <v>790</v>
       </c>
@@ -46440,7 +46440,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="792" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:14" ht="17">
       <c r="A792" s="5">
         <v>791</v>
       </c>
@@ -46481,7 +46481,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="793" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:14" ht="17">
       <c r="A793" s="5">
         <v>792</v>
       </c>
@@ -46522,7 +46522,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="794" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:14" ht="17">
       <c r="A794" s="5">
         <v>793</v>
       </c>
@@ -46563,7 +46563,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="795" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:14" ht="17">
       <c r="A795" s="5">
         <v>794</v>
       </c>
@@ -46607,7 +46607,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="796" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:14" ht="17">
       <c r="A796" s="5">
         <v>795</v>
       </c>
@@ -46648,7 +46648,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="797" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:14" ht="17">
       <c r="A797" s="5">
         <v>796</v>
       </c>
@@ -46689,7 +46689,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="798" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:14" ht="17">
       <c r="A798" s="5">
         <v>797</v>
       </c>
@@ -46730,7 +46730,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="799" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:14" ht="17">
       <c r="A799" s="5">
         <v>798</v>
       </c>
@@ -46771,7 +46771,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="800" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:14" ht="17">
       <c r="A800" s="5">
         <v>799</v>
       </c>
@@ -46812,7 +46812,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="801" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:14" ht="17">
       <c r="A801" s="5">
         <v>800</v>
       </c>
@@ -46853,7 +46853,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="802" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:14" ht="17">
       <c r="A802" s="5">
         <v>801</v>
       </c>
@@ -46894,7 +46894,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="803" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:14" ht="17">
       <c r="A803" s="5">
         <v>802</v>
       </c>
@@ -46935,7 +46935,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="804" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:14" ht="17">
       <c r="A804" s="5">
         <v>803</v>
       </c>
@@ -46976,7 +46976,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="805" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:14" ht="17">
       <c r="A805" s="5">
         <v>804</v>
       </c>
@@ -47017,7 +47017,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="806" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:14" ht="17">
       <c r="A806" s="5">
         <v>805</v>
       </c>
@@ -47058,7 +47058,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="807" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:14" ht="17">
       <c r="A807" s="5">
         <v>806</v>
       </c>
@@ -47099,7 +47099,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="808" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:14" ht="17">
       <c r="A808" s="5">
         <v>807</v>
       </c>
@@ -47140,7 +47140,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="809" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:14" ht="17">
       <c r="A809" s="5">
         <v>808</v>
       </c>
@@ -47181,7 +47181,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="810" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:14" ht="17">
       <c r="A810" s="5">
         <v>809</v>
       </c>
@@ -47222,7 +47222,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="811" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:14" ht="17">
       <c r="A811" s="5">
         <v>810</v>
       </c>
@@ -47263,7 +47263,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="812" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:14" ht="17">
       <c r="A812" s="5">
         <v>811</v>
       </c>
@@ -47304,7 +47304,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="813" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:14" ht="17">
       <c r="A813" s="5">
         <v>812</v>
       </c>
@@ -47345,7 +47345,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="814" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:14" ht="17">
       <c r="A814" s="5">
         <v>813</v>
       </c>
@@ -47386,7 +47386,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="815" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:14" ht="17">
       <c r="A815" s="5">
         <v>814</v>
       </c>
@@ -47427,7 +47427,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="816" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:14" ht="17">
       <c r="A816" s="5">
         <v>815</v>
       </c>
@@ -47468,7 +47468,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="817" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:14" ht="17">
       <c r="A817" s="5">
         <v>816</v>
       </c>
@@ -47509,7 +47509,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="818" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:14" ht="17">
       <c r="A818" s="5">
         <v>817</v>
       </c>
@@ -47550,7 +47550,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="819" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:14" ht="17">
       <c r="A819" s="5">
         <v>818</v>
       </c>
@@ -47591,7 +47591,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="820" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:14" ht="17">
       <c r="A820" s="5">
         <v>819</v>
       </c>
@@ -47632,7 +47632,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="821" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:14" ht="17">
       <c r="A821" s="5">
         <v>820</v>
       </c>
@@ -47673,7 +47673,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="822" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:14" ht="17">
       <c r="A822" s="5">
         <v>821</v>
       </c>
@@ -47714,7 +47714,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="823" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:14" ht="17">
       <c r="A823" s="5">
         <v>822</v>
       </c>
@@ -47755,7 +47755,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="824" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:14" ht="17">
       <c r="A824" s="5">
         <v>823</v>
       </c>
@@ -47796,7 +47796,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="825" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:14" ht="17">
       <c r="A825" s="5">
         <v>824</v>
       </c>
@@ -47837,7 +47837,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="826" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:14" ht="17">
       <c r="A826" s="5">
         <v>825</v>
       </c>
@@ -47878,7 +47878,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="827" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:14" ht="17">
       <c r="A827" s="5">
         <v>826</v>
       </c>
@@ -47919,7 +47919,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="828" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:14" ht="17">
       <c r="A828" s="5">
         <v>827</v>
       </c>
@@ -47960,7 +47960,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="829" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:14" ht="17">
       <c r="A829" s="5">
         <v>828</v>
       </c>
@@ -48001,7 +48001,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="830" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:14" ht="17">
       <c r="A830" s="5">
         <v>829</v>
       </c>
@@ -48042,7 +48042,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="831" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:14" ht="17">
       <c r="A831" s="5">
         <v>830</v>
       </c>
@@ -48083,7 +48083,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="832" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:14" ht="17">
       <c r="A832" s="5">
         <v>831</v>
       </c>
@@ -48124,7 +48124,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="833" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:15" ht="17">
       <c r="A833" s="5">
         <v>832</v>
       </c>
@@ -48165,7 +48165,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="834" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:15" ht="17">
       <c r="A834" s="5">
         <v>833</v>
       </c>
@@ -48206,7 +48206,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="835" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:15" ht="17">
       <c r="A835" s="5">
         <v>834</v>
       </c>
@@ -48247,7 +48247,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="836" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:15" ht="17">
       <c r="A836" s="5">
         <v>835</v>
       </c>
@@ -48291,7 +48291,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="837" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:15" ht="17">
       <c r="A837" s="5">
         <v>836</v>
       </c>
@@ -48335,7 +48335,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="838" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:15" ht="17">
       <c r="A838" s="5">
         <v>837</v>
       </c>
@@ -48379,7 +48379,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="839" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:15" ht="17">
       <c r="A839" s="5">
         <v>838</v>
       </c>
@@ -48423,7 +48423,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="840" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:15" ht="17">
       <c r="A840" s="5">
         <v>839</v>
       </c>
@@ -48467,7 +48467,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="841" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:15" ht="17">
       <c r="A841" s="5">
         <v>840</v>
       </c>
@@ -48511,7 +48511,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="842" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:15" ht="17">
       <c r="A842" s="5">
         <v>841</v>
       </c>
@@ -48555,7 +48555,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="843" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:15" ht="17">
       <c r="A843" s="5">
         <v>842</v>
       </c>
@@ -48599,7 +48599,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="844" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:15" ht="17">
       <c r="A844" s="5">
         <v>843</v>
       </c>
@@ -48640,7 +48640,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="845" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:15" ht="17">
       <c r="A845" s="5">
         <v>844</v>
       </c>
@@ -48681,7 +48681,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="846" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:15" ht="17">
       <c r="A846" s="5">
         <v>845</v>
       </c>
@@ -48722,7 +48722,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="847" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:15" ht="17">
       <c r="A847" s="5">
         <v>846</v>
       </c>
@@ -48763,7 +48763,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="848" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:15" ht="17">
       <c r="A848" s="5">
         <v>847</v>
       </c>
@@ -48804,7 +48804,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="849" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:15" ht="17">
       <c r="A849" s="5">
         <v>848</v>
       </c>
@@ -48845,7 +48845,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="850" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:15" ht="17">
       <c r="A850" s="5">
         <v>849</v>
       </c>
@@ -48886,7 +48886,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="851" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:15" ht="17">
       <c r="A851" s="5">
         <v>850</v>
       </c>
@@ -48927,7 +48927,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="852" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:15" ht="17">
       <c r="A852" s="5">
         <v>851</v>
       </c>
@@ -48968,7 +48968,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="853" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:15" ht="17">
       <c r="A853" s="5">
         <v>852</v>
       </c>
@@ -49009,7 +49009,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="854" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:15" ht="17">
       <c r="A854" s="5">
         <v>853</v>
       </c>
@@ -49047,7 +49047,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="855" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:15" ht="17">
       <c r="A855" s="5">
         <v>854</v>
       </c>
@@ -49085,7 +49085,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="856" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:15">
       <c r="B856" s="6" t="s">
         <v>852</v>
       </c>
@@ -49117,7 +49117,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="857" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:15">
       <c r="B857" s="6" t="s">
         <v>852</v>
       </c>
@@ -49149,7 +49149,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="858" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:15">
       <c r="B858" s="6" t="s">
         <v>852</v>
       </c>
@@ -49193,9 +49193,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0177C972-1D74-9245-AC41-04BB1478BDD0}">
   <dimension ref="B2:J118"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -49224,7 +49224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:10">
       <c r="B3" t="s">
         <v>129</v>
       </c>
@@ -49250,7 +49250,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>129</v>
       </c>
@@ -49276,7 +49276,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:10">
       <c r="B5" t="s">
         <v>129</v>
       </c>
@@ -49302,7 +49302,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10">
       <c r="B6" t="s">
         <v>129</v>
       </c>
@@ -49328,7 +49328,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>129</v>
       </c>
@@ -49354,7 +49354,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10">
       <c r="B8" t="s">
         <v>129</v>
       </c>
@@ -49380,7 +49380,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10">
       <c r="B9" t="s">
         <v>129</v>
       </c>
@@ -49406,7 +49406,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:10">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -49432,7 +49432,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10">
       <c r="B11" t="s">
         <v>129</v>
       </c>
@@ -49458,7 +49458,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10">
       <c r="B12" t="s">
         <v>129</v>
       </c>
@@ -49484,7 +49484,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
         <v>129</v>
       </c>
@@ -49510,7 +49510,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:10">
       <c r="B14" t="s">
         <v>129</v>
       </c>
@@ -49536,7 +49536,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:10">
       <c r="B15" t="s">
         <v>129</v>
       </c>
@@ -49562,7 +49562,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:10">
       <c r="B16" t="s">
         <v>129</v>
       </c>
@@ -49588,7 +49588,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10">
       <c r="B17" t="s">
         <v>129</v>
       </c>
@@ -49614,7 +49614,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10">
       <c r="B18" t="s">
         <v>129</v>
       </c>
@@ -49640,7 +49640,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10">
       <c r="B19" t="s">
         <v>129</v>
       </c>
@@ -49666,7 +49666,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:10">
       <c r="B20" t="s">
         <v>129</v>
       </c>
@@ -49692,7 +49692,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10">
       <c r="B21" t="s">
         <v>129</v>
       </c>
@@ -49718,7 +49718,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10">
       <c r="B22" t="s">
         <v>129</v>
       </c>
@@ -49744,7 +49744,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10">
       <c r="B23" t="s">
         <v>129</v>
       </c>
@@ -49770,7 +49770,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10">
       <c r="B24" t="s">
         <v>129</v>
       </c>
@@ -49796,7 +49796,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10">
       <c r="B25" t="s">
         <v>129</v>
       </c>
@@ -49822,7 +49822,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10">
       <c r="B26" t="s">
         <v>129</v>
       </c>
@@ -49848,7 +49848,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10">
       <c r="B27" t="s">
         <v>129</v>
       </c>
@@ -49874,7 +49874,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10">
       <c r="B28" t="s">
         <v>129</v>
       </c>
@@ -49900,7 +49900,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10">
       <c r="B29" t="s">
         <v>129</v>
       </c>
@@ -49926,7 +49926,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10">
       <c r="B30" t="s">
         <v>129</v>
       </c>
@@ -49952,7 +49952,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10">
       <c r="B31" t="s">
         <v>129</v>
       </c>
@@ -49978,7 +49978,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10">
       <c r="B32" t="s">
         <v>129</v>
       </c>
@@ -50004,7 +50004,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10">
       <c r="B33" t="s">
         <v>129</v>
       </c>
@@ -50030,7 +50030,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10">
       <c r="B34" t="s">
         <v>129</v>
       </c>
@@ -50056,7 +50056,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:10">
       <c r="B35" t="s">
         <v>129</v>
       </c>
@@ -50082,7 +50082,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:10">
       <c r="B36" t="s">
         <v>129</v>
       </c>
@@ -50108,7 +50108,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:10">
       <c r="B37" t="s">
         <v>129</v>
       </c>
@@ -50134,7 +50134,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:10">
       <c r="B38" t="s">
         <v>129</v>
       </c>
@@ -50160,7 +50160,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>129</v>
       </c>
@@ -50186,7 +50186,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:10">
       <c r="B40" t="s">
         <v>129</v>
       </c>
@@ -50212,7 +50212,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:10">
       <c r="B41" t="s">
         <v>129</v>
       </c>
@@ -50238,7 +50238,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:10">
       <c r="B42" t="s">
         <v>129</v>
       </c>
@@ -50264,7 +50264,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:10">
       <c r="B43" t="s">
         <v>129</v>
       </c>
@@ -50290,7 +50290,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:10">
       <c r="B44" t="s">
         <v>129</v>
       </c>
@@ -50316,7 +50316,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:10">
       <c r="B45" t="s">
         <v>129</v>
       </c>
@@ -50342,7 +50342,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:10">
       <c r="B46" t="s">
         <v>129</v>
       </c>
@@ -50368,7 +50368,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:10">
       <c r="B47" t="s">
         <v>129</v>
       </c>
@@ -50394,7 +50394,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:10">
       <c r="B48" t="s">
         <v>129</v>
       </c>
@@ -50420,7 +50420,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:10">
       <c r="B49" t="s">
         <v>129</v>
       </c>
@@ -50446,7 +50446,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:10">
       <c r="B50" t="s">
         <v>129</v>
       </c>
@@ -50472,7 +50472,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:10">
       <c r="B51" t="s">
         <v>129</v>
       </c>
@@ -50498,7 +50498,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:10">
       <c r="B52" t="s">
         <v>129</v>
       </c>
@@ -50524,7 +50524,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:10">
       <c r="B53" t="s">
         <v>129</v>
       </c>
@@ -50550,7 +50550,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:10">
       <c r="B54" t="s">
         <v>129</v>
       </c>
@@ -50576,7 +50576,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:10">
       <c r="B55" t="s">
         <v>129</v>
       </c>
@@ -50602,7 +50602,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:10">
       <c r="B56" t="s">
         <v>129</v>
       </c>
@@ -50629,7 +50629,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:10">
       <c r="B57" t="s">
         <v>129</v>
       </c>
@@ -50656,7 +50656,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:10">
       <c r="B58" t="s">
         <v>129</v>
       </c>
@@ -50683,7 +50683,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:10">
       <c r="B59" t="s">
         <v>129</v>
       </c>
@@ -50710,7 +50710,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:10">
       <c r="B60" t="s">
         <v>129</v>
       </c>
@@ -50737,7 +50737,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:10">
       <c r="B61" t="s">
         <v>129</v>
       </c>
@@ -50764,7 +50764,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:10">
       <c r="B62" t="s">
         <v>129</v>
       </c>
@@ -50791,7 +50791,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:10">
       <c r="B63" t="s">
         <v>129</v>
       </c>
@@ -50818,7 +50818,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:10">
       <c r="B64" t="s">
         <v>129</v>
       </c>
@@ -50845,7 +50845,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:10">
       <c r="B65" t="s">
         <v>129</v>
       </c>
@@ -50872,7 +50872,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:10">
       <c r="B66" t="s">
         <v>129</v>
       </c>
@@ -50899,7 +50899,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:10">
       <c r="B67" t="s">
         <v>129</v>
       </c>
@@ -50926,7 +50926,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:10">
       <c r="B68" t="s">
         <v>129</v>
       </c>
@@ -50953,7 +50953,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:10">
       <c r="B69" t="s">
         <v>129</v>
       </c>
@@ -50980,7 +50980,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:10">
       <c r="B70" t="s">
         <v>129</v>
       </c>
@@ -51007,7 +51007,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:10">
       <c r="B71" t="s">
         <v>129</v>
       </c>
@@ -51034,7 +51034,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:10">
       <c r="B72" t="s">
         <v>129</v>
       </c>
@@ -51061,7 +51061,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:10">
       <c r="B73" t="s">
         <v>129</v>
       </c>
@@ -51088,7 +51088,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:10">
       <c r="B74" t="s">
         <v>129</v>
       </c>
@@ -51115,7 +51115,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:10">
       <c r="B75" t="s">
         <v>129</v>
       </c>
@@ -51142,7 +51142,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:10">
       <c r="B76" t="s">
         <v>129</v>
       </c>
@@ -51169,7 +51169,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:10">
       <c r="B77" t="s">
         <v>129</v>
       </c>
@@ -51196,7 +51196,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:10">
       <c r="B78" t="s">
         <v>129</v>
       </c>
@@ -51223,7 +51223,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:10">
       <c r="B79" t="s">
         <v>129</v>
       </c>
@@ -51250,7 +51250,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:10">
       <c r="B80" t="s">
         <v>129</v>
       </c>
@@ -51277,7 +51277,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:10">
       <c r="B81" t="s">
         <v>129</v>
       </c>
@@ -51304,7 +51304,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:10">
       <c r="B82" t="s">
         <v>129</v>
       </c>
@@ -51331,7 +51331,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:10">
       <c r="B83" t="s">
         <v>129</v>
       </c>
@@ -51358,7 +51358,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:10">
       <c r="B84" t="s">
         <v>129</v>
       </c>
@@ -51385,7 +51385,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:10">
       <c r="B85" t="s">
         <v>129</v>
       </c>
@@ -51412,7 +51412,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:10">
       <c r="B86" t="s">
         <v>129</v>
       </c>
@@ -51439,7 +51439,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:10">
       <c r="B87" t="s">
         <v>129</v>
       </c>
@@ -51466,7 +51466,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:10">
       <c r="B88" t="s">
         <v>129</v>
       </c>
@@ -51493,7 +51493,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:10">
       <c r="B89" t="s">
         <v>129</v>
       </c>
@@ -51520,7 +51520,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:10">
       <c r="B90" t="s">
         <v>129</v>
       </c>
@@ -51547,7 +51547,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:10">
       <c r="B91" t="s">
         <v>129</v>
       </c>
@@ -51574,7 +51574,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:10">
       <c r="B92" t="s">
         <v>129</v>
       </c>
@@ -51601,7 +51601,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:10">
       <c r="B93" t="s">
         <v>129</v>
       </c>
@@ -51628,7 +51628,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:10">
       <c r="B94" t="s">
         <v>129</v>
       </c>
@@ -51655,7 +51655,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:10">
       <c r="B95" t="s">
         <v>129</v>
       </c>
@@ -51682,7 +51682,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:10">
       <c r="B96" t="s">
         <v>129</v>
       </c>
@@ -51709,7 +51709,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:10">
       <c r="B97" t="s">
         <v>129</v>
       </c>
@@ -51736,7 +51736,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:10">
       <c r="B98" t="s">
         <v>129</v>
       </c>
@@ -51763,7 +51763,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:10">
       <c r="B99" t="s">
         <v>129</v>
       </c>
@@ -51790,7 +51790,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:10">
       <c r="B100" t="s">
         <v>129</v>
       </c>
@@ -51816,7 +51816,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:10">
       <c r="B101" t="s">
         <v>129</v>
       </c>
@@ -51842,7 +51842,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:10">
       <c r="B102" t="s">
         <v>129</v>
       </c>
@@ -51868,7 +51868,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:10">
       <c r="B103" t="s">
         <v>129</v>
       </c>
@@ -51894,7 +51894,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:10">
       <c r="B104" t="s">
         <v>129</v>
       </c>
@@ -51920,7 +51920,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:10">
       <c r="B105" t="s">
         <v>129</v>
       </c>
@@ -51946,7 +51946,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="106" spans="2:10">
       <c r="B106" t="s">
         <v>129</v>
       </c>
@@ -51972,7 +51972,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:10">
       <c r="B107" t="s">
         <v>129</v>
       </c>
@@ -51998,7 +51998,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="108" spans="2:10">
       <c r="B108" t="s">
         <v>129</v>
       </c>
@@ -52024,7 +52024,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="109" spans="2:10">
       <c r="B109" t="s">
         <v>129</v>
       </c>
@@ -52050,7 +52050,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="110" spans="2:10">
       <c r="B110" t="s">
         <v>129</v>
       </c>
@@ -52076,7 +52076,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:10">
       <c r="B111" t="s">
         <v>129</v>
       </c>
@@ -52102,7 +52102,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="112" spans="2:10">
       <c r="B112" t="s">
         <v>129</v>
       </c>
@@ -52128,7 +52128,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="113" spans="2:10">
       <c r="B113" t="s">
         <v>129</v>
       </c>
@@ -52154,7 +52154,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="114" spans="2:10">
       <c r="B114" t="s">
         <v>129</v>
       </c>
@@ -52180,7 +52180,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="115" spans="2:10">
       <c r="B115" t="s">
         <v>129</v>
       </c>
@@ -52206,7 +52206,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="116" spans="2:10">
       <c r="B116" t="s">
         <v>129</v>
       </c>
@@ -52232,7 +52232,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="117" spans="2:10">
       <c r="B117" t="s">
         <v>129</v>
       </c>
@@ -52258,7 +52258,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="118" spans="2:10">
       <c r="B118" t="s">
         <v>129</v>
       </c>

--- a/data_lake/metadata.xlsx
+++ b/data_lake/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C664AF-039C-4D6B-B8C5-E9DFA477400D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14136733-8F8E-443F-8422-3A0F5F06AAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11118" uniqueCount="2476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11129" uniqueCount="2480">
   <si>
     <t>ASSET_CLASS</t>
   </si>
@@ -14120,6 +14120,22 @@
       </rPr>
       <t>내재 상관지수</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BVSPVIX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brazil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S&amp;P/B3 IBOVESPA VIX Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -14547,7 +14563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O861"/>
+  <dimension ref="A1:O862"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="5"/>
@@ -41972,9 +41988,6 @@
       </c>
     </row>
     <row r="683" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A683" s="5">
-        <v>682</v>
-      </c>
       <c r="B683" s="6" t="s">
         <v>929</v>
       </c>
@@ -41985,22 +41998,19 @@
         <v>128</v>
       </c>
       <c r="F683" s="6" t="s">
-        <v>1032</v>
+        <v>2476</v>
       </c>
       <c r="G683" s="6" t="s">
-        <v>1032</v>
+        <v>2476</v>
       </c>
       <c r="H683" s="6" t="s">
-        <v>1046</v>
+        <v>2477</v>
       </c>
       <c r="I683" s="6" t="s">
-        <v>812</v>
+        <v>2478</v>
       </c>
       <c r="J683" s="6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="K683" s="6" t="s">
-        <v>2292</v>
+        <v>2479</v>
       </c>
       <c r="L683" s="6" t="s">
         <v>741</v>
@@ -42014,34 +42024,34 @@
     </row>
     <row r="684" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A684" s="5">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B684" s="6" t="s">
         <v>929</v>
       </c>
       <c r="C684" s="6" t="s">
-        <v>1055</v>
+        <v>928</v>
       </c>
       <c r="E684" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F684" s="6" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="G684" s="6" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="H684" s="6" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="I684" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J684" s="6" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="K684" s="6" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="L684" s="6" t="s">
         <v>741</v>
@@ -42055,34 +42065,34 @@
     </row>
     <row r="685" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A685" s="5">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B685" s="6" t="s">
         <v>929</v>
       </c>
       <c r="C685" s="6" t="s">
-        <v>435</v>
+        <v>1055</v>
       </c>
       <c r="E685" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F685" s="6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G685" s="6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H685" s="6" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="I685" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J685" s="6" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="K685" s="6" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="L685" s="6" t="s">
         <v>741</v>
@@ -42096,7 +42106,7 @@
     </row>
     <row r="686" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A686" s="5">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B686" s="6" t="s">
         <v>929</v>
@@ -42108,10 +42118,10 @@
         <v>128</v>
       </c>
       <c r="F686" s="6" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G686" s="6" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H686" s="6" t="s">
         <v>1046</v>
@@ -42120,10 +42130,10 @@
         <v>812</v>
       </c>
       <c r="J686" s="6" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K686" s="6" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="L686" s="6" t="s">
         <v>741</v>
@@ -42137,7 +42147,7 @@
     </row>
     <row r="687" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A687" s="5">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B687" s="6" t="s">
         <v>929</v>
@@ -42149,10 +42159,10 @@
         <v>128</v>
       </c>
       <c r="F687" s="6" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G687" s="6" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="H687" s="6" t="s">
         <v>1046</v>
@@ -42161,10 +42171,10 @@
         <v>812</v>
       </c>
       <c r="J687" s="6" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="K687" s="6" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="L687" s="6" t="s">
         <v>741</v>
@@ -42178,7 +42188,7 @@
     </row>
     <row r="688" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A688" s="5">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B688" s="6" t="s">
         <v>929</v>
@@ -42190,10 +42200,10 @@
         <v>128</v>
       </c>
       <c r="F688" s="6" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G688" s="6" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H688" s="6" t="s">
         <v>1046</v>
@@ -42202,10 +42212,10 @@
         <v>812</v>
       </c>
       <c r="J688" s="6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="K688" s="6" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="L688" s="6" t="s">
         <v>741</v>
@@ -42219,22 +42229,22 @@
     </row>
     <row r="689" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A689" s="5">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B689" s="6" t="s">
         <v>929</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>1056</v>
+        <v>435</v>
       </c>
       <c r="E689" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F689" s="6" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G689" s="6" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H689" s="6" t="s">
         <v>1046</v>
@@ -42243,10 +42253,10 @@
         <v>812</v>
       </c>
       <c r="J689" s="6" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="K689" s="6" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="L689" s="6" t="s">
         <v>741</v>
@@ -42260,22 +42270,22 @@
     </row>
     <row r="690" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A690" s="5">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B690" s="6" t="s">
         <v>929</v>
       </c>
       <c r="C690" s="6" t="s">
-        <v>928</v>
+        <v>1056</v>
       </c>
       <c r="E690" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F690" s="6" t="s">
-        <v>1628</v>
+        <v>1035</v>
       </c>
       <c r="G690" s="6" t="s">
-        <v>1628</v>
+        <v>1035</v>
       </c>
       <c r="H690" s="6" t="s">
         <v>1046</v>
@@ -42284,10 +42294,10 @@
         <v>812</v>
       </c>
       <c r="J690" s="6" t="s">
-        <v>1648</v>
+        <v>1054</v>
       </c>
       <c r="K690" s="6" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="L690" s="6" t="s">
         <v>741</v>
@@ -42301,7 +42311,7 @@
     </row>
     <row r="691" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A691" s="5">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B691" s="6" t="s">
         <v>929</v>
@@ -42313,22 +42323,22 @@
         <v>128</v>
       </c>
       <c r="F691" s="6" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="G691" s="6" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H691" s="6" t="s">
-        <v>1630</v>
+        <v>1046</v>
       </c>
       <c r="I691" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J691" s="6" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="K691" s="6" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="L691" s="6" t="s">
         <v>741</v>
@@ -42342,7 +42352,7 @@
     </row>
     <row r="692" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A692" s="5">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B692" s="6" t="s">
         <v>929</v>
@@ -42354,22 +42364,22 @@
         <v>128</v>
       </c>
       <c r="F692" s="6" t="s">
-        <v>1645</v>
+        <v>1629</v>
       </c>
       <c r="G692" s="6" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="H692" s="6" t="s">
-        <v>128</v>
+        <v>1630</v>
       </c>
       <c r="I692" s="6" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="J692" s="6" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="K692" s="6" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="L692" s="6" t="s">
         <v>741</v>
@@ -42383,7 +42393,7 @@
     </row>
     <row r="693" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A693" s="5">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B693" s="6" t="s">
         <v>929</v>
@@ -42395,22 +42405,22 @@
         <v>128</v>
       </c>
       <c r="F693" s="6" t="s">
-        <v>1632</v>
+        <v>1645</v>
       </c>
       <c r="G693" s="6" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H693" s="6" t="s">
-        <v>1633</v>
+        <v>128</v>
       </c>
       <c r="I693" s="6" t="s">
-        <v>1380</v>
+        <v>815</v>
       </c>
       <c r="J693" s="6" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="K693" s="6" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="L693" s="6" t="s">
         <v>741</v>
@@ -42424,7 +42434,7 @@
     </row>
     <row r="694" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A694" s="5">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B694" s="6" t="s">
         <v>929</v>
@@ -42436,22 +42446,22 @@
         <v>128</v>
       </c>
       <c r="F694" s="6" t="s">
-        <v>1646</v>
+        <v>1632</v>
       </c>
       <c r="G694" s="6" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="H694" s="6" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="I694" s="6" t="s">
-        <v>1644</v>
+        <v>1380</v>
       </c>
       <c r="J694" s="6" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="K694" s="6" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="L694" s="6" t="s">
         <v>741</v>
@@ -42465,7 +42475,7 @@
     </row>
     <row r="695" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A695" s="5">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B695" s="6" t="s">
         <v>929</v>
@@ -42477,22 +42487,22 @@
         <v>128</v>
       </c>
       <c r="F695" s="6" t="s">
-        <v>1636</v>
+        <v>1646</v>
       </c>
       <c r="G695" s="6" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="H695" s="6" t="s">
-        <v>1046</v>
+        <v>1635</v>
       </c>
       <c r="I695" s="6" t="s">
-        <v>812</v>
+        <v>1644</v>
       </c>
       <c r="J695" s="6" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="K695" s="6" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="L695" s="6" t="s">
         <v>741</v>
@@ -42506,7 +42516,7 @@
     </row>
     <row r="696" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A696" s="5">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B696" s="6" t="s">
         <v>929</v>
@@ -42518,10 +42528,10 @@
         <v>128</v>
       </c>
       <c r="F696" s="6" t="s">
-        <v>1647</v>
+        <v>1636</v>
       </c>
       <c r="G696" s="6" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H696" s="6" t="s">
         <v>1046</v>
@@ -42530,10 +42540,10 @@
         <v>812</v>
       </c>
       <c r="J696" s="6" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="K696" s="6" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="L696" s="6" t="s">
         <v>741</v>
@@ -42547,34 +42557,34 @@
     </row>
     <row r="697" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A697" s="5">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B697" s="6" t="s">
-        <v>435</v>
+        <v>929</v>
       </c>
       <c r="C697" s="6" t="s">
-        <v>1179</v>
+        <v>928</v>
       </c>
       <c r="E697" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F697" s="6" t="s">
-        <v>1064</v>
+        <v>1647</v>
       </c>
       <c r="G697" s="6" t="s">
-        <v>1076</v>
+        <v>1637</v>
       </c>
       <c r="H697" s="6" t="s">
-        <v>1078</v>
+        <v>1046</v>
       </c>
       <c r="I697" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J697" s="6" t="s">
-        <v>1093</v>
+        <v>1638</v>
       </c>
       <c r="K697" s="6" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="L697" s="6" t="s">
         <v>741</v>
@@ -42588,7 +42598,7 @@
     </row>
     <row r="698" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A698" s="5">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B698" s="6" t="s">
         <v>435</v>
@@ -42600,22 +42610,22 @@
         <v>128</v>
       </c>
       <c r="F698" s="6" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G698" s="6" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H698" s="6" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I698" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J698" s="6" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="K698" s="6" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="L698" s="6" t="s">
         <v>741</v>
@@ -42629,7 +42639,7 @@
     </row>
     <row r="699" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A699" s="5">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B699" s="6" t="s">
         <v>435</v>
@@ -42641,22 +42651,22 @@
         <v>128</v>
       </c>
       <c r="F699" s="6" t="s">
-        <v>1081</v>
+        <v>1065</v>
       </c>
       <c r="G699" s="6" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="H699" s="6" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="I699" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J699" s="6" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="K699" s="6" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="L699" s="6" t="s">
         <v>741</v>
@@ -42665,33 +42675,27 @@
         <v>389</v>
       </c>
       <c r="N699" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="O699" s="6" t="s">
-        <v>1101</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="700" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A700" s="5">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B700" s="6" t="s">
         <v>435</v>
       </c>
       <c r="C700" s="6" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D700" s="6" t="s">
-        <v>1096</v>
+        <v>1179</v>
       </c>
       <c r="E700" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F700" s="6" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="G700" s="6" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="H700" s="6" t="s">
         <v>1079</v>
@@ -42700,10 +42704,10 @@
         <v>812</v>
       </c>
       <c r="J700" s="6" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="K700" s="6" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="L700" s="6" t="s">
         <v>741</v>
@@ -42712,30 +42716,33 @@
         <v>389</v>
       </c>
       <c r="N700" s="6" t="s">
-        <v>1036</v>
+        <v>450</v>
+      </c>
+      <c r="O700" s="6" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="701" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A701" s="5">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B701" s="6" t="s">
         <v>435</v>
       </c>
       <c r="C701" s="6" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D701" s="6" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E701" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F701" s="6" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G701" s="6" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H701" s="6" t="s">
         <v>1079</v>
@@ -42744,10 +42751,10 @@
         <v>812</v>
       </c>
       <c r="J701" s="6" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="K701" s="6" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="L701" s="6" t="s">
         <v>741</v>
@@ -42761,7 +42768,7 @@
     </row>
     <row r="702" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A702" s="5">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B702" s="6" t="s">
         <v>435</v>
@@ -42776,10 +42783,10 @@
         <v>128</v>
       </c>
       <c r="F702" s="6" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G702" s="6" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H702" s="6" t="s">
         <v>1079</v>
@@ -42788,10 +42795,10 @@
         <v>812</v>
       </c>
       <c r="J702" s="6" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="K702" s="6" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="L702" s="6" t="s">
         <v>741</v>
@@ -42805,7 +42812,7 @@
     </row>
     <row r="703" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A703" s="5">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B703" s="6" t="s">
         <v>435</v>
@@ -42814,16 +42821,16 @@
         <v>1097</v>
       </c>
       <c r="D703" s="6" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E703" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F703" s="6" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G703" s="6" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H703" s="6" t="s">
         <v>1079</v>
@@ -42832,10 +42839,10 @@
         <v>812</v>
       </c>
       <c r="J703" s="6" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="K703" s="6" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="L703" s="6" t="s">
         <v>741</v>
@@ -42849,7 +42856,7 @@
     </row>
     <row r="704" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A704" s="5">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B704" s="6" t="s">
         <v>435</v>
@@ -42858,16 +42865,16 @@
         <v>1097</v>
       </c>
       <c r="D704" s="6" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E704" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F704" s="6" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G704" s="6" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H704" s="6" t="s">
         <v>1079</v>
@@ -42876,10 +42883,10 @@
         <v>812</v>
       </c>
       <c r="J704" s="6" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="K704" s="6" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="L704" s="6" t="s">
         <v>741</v>
@@ -42893,25 +42900,25 @@
     </row>
     <row r="705" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A705" s="5">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B705" s="6" t="s">
         <v>435</v>
       </c>
       <c r="C705" s="6" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D705" s="6" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="E705" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F705" s="6" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G705" s="6" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H705" s="6" t="s">
         <v>1079</v>
@@ -42920,10 +42927,10 @@
         <v>812</v>
       </c>
       <c r="J705" s="6" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="K705" s="6" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="L705" s="6" t="s">
         <v>741</v>
@@ -42937,7 +42944,7 @@
     </row>
     <row r="706" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A706" s="5">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B706" s="6" t="s">
         <v>435</v>
@@ -42946,16 +42953,16 @@
         <v>1095</v>
       </c>
       <c r="D706" s="6" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="E706" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F706" s="6" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G706" s="6" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H706" s="6" t="s">
         <v>1079</v>
@@ -42964,10 +42971,10 @@
         <v>812</v>
       </c>
       <c r="J706" s="6" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="K706" s="6" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="L706" s="6" t="s">
         <v>741</v>
@@ -42981,22 +42988,25 @@
     </row>
     <row r="707" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A707" s="5">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B707" s="6" t="s">
         <v>435</v>
       </c>
       <c r="C707" s="6" t="s">
-        <v>436</v>
+        <v>1095</v>
+      </c>
+      <c r="D707" s="6" t="s">
+        <v>1100</v>
       </c>
       <c r="E707" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F707" s="6" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G707" s="6" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H707" s="6" t="s">
         <v>1079</v>
@@ -43005,10 +43015,10 @@
         <v>812</v>
       </c>
       <c r="J707" s="6" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="K707" s="6" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="L707" s="6" t="s">
         <v>741</v>
@@ -43022,25 +43032,22 @@
     </row>
     <row r="708" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A708" s="5">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B708" s="6" t="s">
         <v>435</v>
       </c>
       <c r="C708" s="6" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D708" s="6" t="s">
-        <v>1099</v>
+        <v>436</v>
       </c>
       <c r="E708" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F708" s="6" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G708" s="6" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H708" s="6" t="s">
         <v>1079</v>
@@ -43049,10 +43056,10 @@
         <v>812</v>
       </c>
       <c r="J708" s="6" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="K708" s="6" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="L708" s="6" t="s">
         <v>741</v>
@@ -43066,7 +43073,7 @@
     </row>
     <row r="709" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A709" s="5">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B709" s="6" t="s">
         <v>435</v>
@@ -43074,14 +43081,17 @@
       <c r="C709" s="6" t="s">
         <v>1097</v>
       </c>
+      <c r="D709" s="6" t="s">
+        <v>1099</v>
+      </c>
       <c r="E709" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F709" s="6" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G709" s="6" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H709" s="6" t="s">
         <v>1079</v>
@@ -43090,10 +43100,10 @@
         <v>812</v>
       </c>
       <c r="J709" s="6" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="K709" s="6" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="L709" s="6" t="s">
         <v>741</v>
@@ -43107,51 +43117,48 @@
     </row>
     <row r="710" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A710" s="5">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B710" s="6" t="s">
-        <v>852</v>
+        <v>435</v>
       </c>
       <c r="C710" s="6" t="s">
-        <v>928</v>
-      </c>
-      <c r="D710" s="6" t="s">
-        <v>853</v>
+        <v>1097</v>
       </c>
       <c r="E710" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F710" s="6" t="s">
-        <v>1109</v>
+        <v>1075</v>
+      </c>
+      <c r="G710" s="6" t="s">
+        <v>1075</v>
       </c>
       <c r="H710" s="6" t="s">
-        <v>1104</v>
+        <v>1079</v>
       </c>
       <c r="I710" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J710" s="6" t="s">
-        <v>1106</v>
+        <v>1092</v>
       </c>
       <c r="K710" s="6" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="L710" s="6" t="s">
-        <v>840</v>
+        <v>741</v>
       </c>
       <c r="M710" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N710" s="6" t="s">
-        <v>1104</v>
-      </c>
-      <c r="O710" s="6" t="s">
-        <v>1105</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="711" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A711" s="5">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B711" s="6" t="s">
         <v>852</v>
@@ -43166,7 +43173,7 @@
         <v>128</v>
       </c>
       <c r="F711" s="6" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H711" s="6" t="s">
         <v>1104</v>
@@ -43175,10 +43182,10 @@
         <v>812</v>
       </c>
       <c r="J711" s="6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K711" s="6" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="L711" s="6" t="s">
         <v>840</v>
@@ -43195,7 +43202,7 @@
     </row>
     <row r="712" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A712" s="5">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B712" s="6" t="s">
         <v>852</v>
@@ -43210,7 +43217,7 @@
         <v>128</v>
       </c>
       <c r="F712" s="6" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H712" s="6" t="s">
         <v>1104</v>
@@ -43219,10 +43226,10 @@
         <v>812</v>
       </c>
       <c r="J712" s="6" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="K712" s="6" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="L712" s="6" t="s">
         <v>840</v>
@@ -43239,7 +43246,7 @@
     </row>
     <row r="713" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A713" s="5">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B713" s="6" t="s">
         <v>852</v>
@@ -43248,45 +43255,42 @@
         <v>928</v>
       </c>
       <c r="D713" s="6" t="s">
-        <v>1102</v>
+        <v>853</v>
       </c>
       <c r="E713" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F713" s="6" t="s">
-        <v>1112</v>
-      </c>
-      <c r="G713" s="6" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H713" s="6" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
       <c r="I713" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J713" s="6" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="K713" s="6" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="L713" s="6" t="s">
-        <v>741</v>
+        <v>840</v>
       </c>
       <c r="M713" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N713" s="6" t="s">
-        <v>1115</v>
+        <v>1104</v>
       </c>
       <c r="O713" s="6" t="s">
-        <v>1114</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="714" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A714" s="5">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B714" s="6" t="s">
         <v>852</v>
@@ -43301,36 +43305,39 @@
         <v>128</v>
       </c>
       <c r="F714" s="6" t="s">
-        <v>1119</v>
+        <v>1112</v>
+      </c>
+      <c r="G714" s="6" t="s">
+        <v>1112</v>
       </c>
       <c r="H714" s="6" t="s">
-        <v>444</v>
+        <v>1113</v>
       </c>
       <c r="I714" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J714" s="6" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="K714" s="6" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="L714" s="6" t="s">
         <v>741</v>
       </c>
       <c r="M714" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N714" s="6" t="s">
-        <v>444</v>
+        <v>1115</v>
       </c>
       <c r="O714" s="6" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="715" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A715" s="5">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B715" s="6" t="s">
         <v>852</v>
@@ -43339,25 +43346,25 @@
         <v>928</v>
       </c>
       <c r="D715" s="6" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E715" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F715" s="6" t="s">
-        <v>1129</v>
+        <v>1119</v>
       </c>
       <c r="H715" s="6" t="s">
-        <v>1120</v>
+        <v>444</v>
       </c>
       <c r="I715" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J715" s="6" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="K715" s="6" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="L715" s="6" t="s">
         <v>741</v>
@@ -43366,15 +43373,15 @@
         <v>388</v>
       </c>
       <c r="N715" s="6" t="s">
-        <v>1120</v>
+        <v>444</v>
       </c>
       <c r="O715" s="6" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="716" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A716" s="5">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B716" s="6" t="s">
         <v>852</v>
@@ -43389,7 +43396,7 @@
         <v>128</v>
       </c>
       <c r="F716" s="6" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H716" s="6" t="s">
         <v>1120</v>
@@ -43398,7 +43405,10 @@
         <v>812</v>
       </c>
       <c r="J716" s="6" t="s">
-        <v>1122</v>
+        <v>1121</v>
+      </c>
+      <c r="K716" s="6" t="s">
+        <v>2324</v>
       </c>
       <c r="L716" s="6" t="s">
         <v>741</v>
@@ -43415,7 +43425,7 @@
     </row>
     <row r="717" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A717" s="5">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B717" s="6" t="s">
         <v>852</v>
@@ -43430,7 +43440,7 @@
         <v>128</v>
       </c>
       <c r="F717" s="6" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="H717" s="6" t="s">
         <v>1120</v>
@@ -43439,7 +43449,7 @@
         <v>812</v>
       </c>
       <c r="J717" s="6" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="L717" s="6" t="s">
         <v>741</v>
@@ -43456,7 +43466,7 @@
     </row>
     <row r="718" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A718" s="5">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B718" s="6" t="s">
         <v>852</v>
@@ -43471,7 +43481,7 @@
         <v>128</v>
       </c>
       <c r="F718" s="6" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="H718" s="6" t="s">
         <v>1120</v>
@@ -43480,7 +43490,7 @@
         <v>812</v>
       </c>
       <c r="J718" s="6" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="L718" s="6" t="s">
         <v>741</v>
@@ -43497,7 +43507,7 @@
     </row>
     <row r="719" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A719" s="5">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B719" s="6" t="s">
         <v>852</v>
@@ -43512,7 +43522,7 @@
         <v>128</v>
       </c>
       <c r="F719" s="6" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="H719" s="6" t="s">
         <v>1120</v>
@@ -43521,7 +43531,7 @@
         <v>812</v>
       </c>
       <c r="J719" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="L719" s="6" t="s">
         <v>741</v>
@@ -43538,7 +43548,7 @@
     </row>
     <row r="720" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A720" s="5">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B720" s="6" t="s">
         <v>852</v>
@@ -43553,7 +43563,7 @@
         <v>128</v>
       </c>
       <c r="F720" s="6" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="H720" s="6" t="s">
         <v>1120</v>
@@ -43562,7 +43572,7 @@
         <v>812</v>
       </c>
       <c r="J720" s="6" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L720" s="6" t="s">
         <v>741</v>
@@ -43579,7 +43589,7 @@
     </row>
     <row r="721" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A721" s="5">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B721" s="6" t="s">
         <v>852</v>
@@ -43594,7 +43604,7 @@
         <v>128</v>
       </c>
       <c r="F721" s="6" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H721" s="6" t="s">
         <v>1120</v>
@@ -43603,7 +43613,7 @@
         <v>812</v>
       </c>
       <c r="J721" s="6" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L721" s="6" t="s">
         <v>741</v>
@@ -43618,65 +43628,65 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="722" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A722" s="5">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B722" s="6" t="s">
-        <v>446</v>
+        <v>852</v>
       </c>
       <c r="C722" s="6" t="s">
-        <v>1179</v>
+        <v>928</v>
+      </c>
+      <c r="D722" s="6" t="s">
+        <v>1103</v>
       </c>
       <c r="E722" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F722" s="6" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G722" s="6" t="s">
-        <v>1157</v>
+        <v>1133</v>
       </c>
       <c r="H722" s="6" t="s">
-        <v>1045</v>
+        <v>1120</v>
       </c>
       <c r="I722" s="6" t="s">
-        <v>470</v>
+        <v>812</v>
       </c>
       <c r="J722" s="6" t="s">
-        <v>1136</v>
-      </c>
-      <c r="K722" s="6" t="s">
-        <v>2325</v>
+        <v>1127</v>
       </c>
       <c r="L722" s="6" t="s">
         <v>741</v>
       </c>
       <c r="M722" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N722" s="6" t="s">
-        <v>1036</v>
+        <v>1120</v>
+      </c>
+      <c r="O722" s="6" t="s">
+        <v>1128</v>
       </c>
     </row>
     <row r="723" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A723" s="5">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B723" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C723" s="6" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E723" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F723" s="6" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G723" s="6" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="H723" s="6" t="s">
         <v>1045</v>
@@ -43685,10 +43695,10 @@
         <v>470</v>
       </c>
       <c r="J723" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K723" s="6" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="L723" s="6" t="s">
         <v>741</v>
@@ -43702,22 +43712,22 @@
     </row>
     <row r="724" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A724" s="5">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B724" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C724" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E724" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F724" s="6" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G724" s="6" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H724" s="6" t="s">
         <v>1045</v>
@@ -43726,10 +43736,10 @@
         <v>470</v>
       </c>
       <c r="J724" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="K724" s="6" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="L724" s="6" t="s">
         <v>741</v>
@@ -43743,22 +43753,22 @@
     </row>
     <row r="725" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A725" s="5">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B725" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C725" s="6" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E725" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F725" s="6" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="G725" s="6" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H725" s="6" t="s">
         <v>1045</v>
@@ -43767,10 +43777,10 @@
         <v>470</v>
       </c>
       <c r="J725" s="6" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K725" s="6" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L725" s="6" t="s">
         <v>741</v>
@@ -43784,7 +43794,7 @@
     </row>
     <row r="726" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A726" s="5">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B726" s="6" t="s">
         <v>446</v>
@@ -43796,10 +43806,10 @@
         <v>128</v>
       </c>
       <c r="F726" s="6" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G726" s="6" t="s">
-        <v>1178</v>
+        <v>1160</v>
       </c>
       <c r="H726" s="6" t="s">
         <v>1045</v>
@@ -43808,10 +43818,10 @@
         <v>470</v>
       </c>
       <c r="J726" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="K726" s="6" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="L726" s="6" t="s">
         <v>741</v>
@@ -43825,22 +43835,22 @@
     </row>
     <row r="727" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A727" s="5">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B727" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C727" s="6" t="s">
-        <v>970</v>
+        <v>1180</v>
       </c>
       <c r="E727" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F727" s="6" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G727" s="6" t="s">
-        <v>1162</v>
+        <v>1178</v>
       </c>
       <c r="H727" s="6" t="s">
         <v>1045</v>
@@ -43849,10 +43859,10 @@
         <v>470</v>
       </c>
       <c r="J727" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K727" s="6" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="L727" s="6" t="s">
         <v>741</v>
@@ -43866,22 +43876,22 @@
     </row>
     <row r="728" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A728" s="5">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B728" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C728" s="6" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="E728" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F728" s="6" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G728" s="6" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H728" s="6" t="s">
         <v>1045</v>
@@ -43890,10 +43900,10 @@
         <v>470</v>
       </c>
       <c r="J728" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K728" s="6" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="L728" s="6" t="s">
         <v>741</v>
@@ -43907,22 +43917,22 @@
     </row>
     <row r="729" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A729" s="5">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B729" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C729" s="6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="E729" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F729" s="6" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G729" s="6" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H729" s="6" t="s">
         <v>1045</v>
@@ -43931,10 +43941,10 @@
         <v>470</v>
       </c>
       <c r="J729" s="6" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="K729" s="6" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="L729" s="6" t="s">
         <v>741</v>
@@ -43948,22 +43958,22 @@
     </row>
     <row r="730" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A730" s="5">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B730" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C730" s="6" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E730" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F730" s="6" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G730" s="6" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H730" s="6" t="s">
         <v>1045</v>
@@ -43972,10 +43982,10 @@
         <v>470</v>
       </c>
       <c r="J730" s="6" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="K730" s="6" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="L730" s="6" t="s">
         <v>741</v>
@@ -43989,22 +43999,22 @@
     </row>
     <row r="731" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A731" s="5">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B731" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C731" s="6" t="s">
-        <v>436</v>
+        <v>974</v>
       </c>
       <c r="E731" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F731" s="6" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G731" s="6" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H731" s="6" t="s">
         <v>1045</v>
@@ -44013,10 +44023,10 @@
         <v>470</v>
       </c>
       <c r="J731" s="6" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="K731" s="6" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L731" s="6" t="s">
         <v>741</v>
@@ -44030,22 +44040,22 @@
     </row>
     <row r="732" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A732" s="5">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B732" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C732" s="6" t="s">
-        <v>969</v>
+        <v>436</v>
       </c>
       <c r="E732" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F732" s="6" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G732" s="6" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H732" s="6" t="s">
         <v>1045</v>
@@ -44054,10 +44064,10 @@
         <v>470</v>
       </c>
       <c r="J732" s="6" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="K732" s="6" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="L732" s="6" t="s">
         <v>741</v>
@@ -44071,22 +44081,22 @@
     </row>
     <row r="733" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A733" s="5">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B733" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C733" s="6" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="E733" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F733" s="6" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G733" s="6" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H733" s="6" t="s">
         <v>1045</v>
@@ -44095,10 +44105,10 @@
         <v>470</v>
       </c>
       <c r="J733" s="6" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K733" s="6" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="L733" s="6" t="s">
         <v>741</v>
@@ -44112,22 +44122,22 @@
     </row>
     <row r="734" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A734" s="5">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B734" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C734" s="6" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="E734" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F734" s="6" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G734" s="6" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H734" s="6" t="s">
         <v>1045</v>
@@ -44136,10 +44146,10 @@
         <v>470</v>
       </c>
       <c r="J734" s="6" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="K734" s="6" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="L734" s="6" t="s">
         <v>741</v>
@@ -44153,22 +44163,22 @@
     </row>
     <row r="735" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A735" s="5">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B735" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C735" s="6" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="E735" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F735" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G735" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H735" s="6" t="s">
         <v>1045</v>
@@ -44177,10 +44187,10 @@
         <v>470</v>
       </c>
       <c r="J735" s="6" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="K735" s="6" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="L735" s="6" t="s">
         <v>741</v>
@@ -44194,22 +44204,22 @@
     </row>
     <row r="736" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A736" s="5">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B736" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C736" s="6" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="E736" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F736" s="6" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G736" s="6" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H736" s="6" t="s">
         <v>1045</v>
@@ -44218,10 +44228,10 @@
         <v>470</v>
       </c>
       <c r="J736" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="K736" s="6" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="L736" s="6" t="s">
         <v>741</v>
@@ -44235,22 +44245,22 @@
     </row>
     <row r="737" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A737" s="5">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B737" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C737" s="6" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="E737" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F737" s="6" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G737" s="6" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H737" s="6" t="s">
         <v>1045</v>
@@ -44259,10 +44269,10 @@
         <v>470</v>
       </c>
       <c r="J737" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K737" s="6" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="L737" s="6" t="s">
         <v>741</v>
@@ -44276,22 +44286,22 @@
     </row>
     <row r="738" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A738" s="5">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B738" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C738" s="6" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="E738" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F738" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G738" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H738" s="6" t="s">
         <v>1045</v>
@@ -44300,10 +44310,10 @@
         <v>470</v>
       </c>
       <c r="J738" s="6" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="K738" s="6" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="L738" s="6" t="s">
         <v>741</v>
@@ -44317,22 +44327,22 @@
     </row>
     <row r="739" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A739" s="5">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B739" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C739" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E739" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F739" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G739" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H739" s="6" t="s">
         <v>1045</v>
@@ -44341,10 +44351,10 @@
         <v>470</v>
       </c>
       <c r="J739" s="6" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="K739" s="6" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="L739" s="6" t="s">
         <v>741</v>
@@ -44358,22 +44368,22 @@
     </row>
     <row r="740" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A740" s="5">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B740" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C740" s="6" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E740" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F740" s="6" t="s">
-        <v>1226</v>
+        <v>1174</v>
       </c>
       <c r="G740" s="6" t="s">
-        <v>1226</v>
+        <v>1174</v>
       </c>
       <c r="H740" s="6" t="s">
         <v>1045</v>
@@ -44382,10 +44392,10 @@
         <v>470</v>
       </c>
       <c r="J740" s="6" t="s">
-        <v>1227</v>
+        <v>1153</v>
       </c>
       <c r="K740" s="6" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="L740" s="6" t="s">
         <v>741</v>
@@ -44399,22 +44409,22 @@
     </row>
     <row r="741" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A741" s="5">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B741" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C741" s="6" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="E741" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F741" s="6" t="s">
-        <v>1175</v>
+        <v>1226</v>
       </c>
       <c r="G741" s="6" t="s">
-        <v>1175</v>
+        <v>1226</v>
       </c>
       <c r="H741" s="6" t="s">
         <v>1045</v>
@@ -44423,10 +44433,10 @@
         <v>470</v>
       </c>
       <c r="J741" s="6" t="s">
-        <v>1154</v>
+        <v>1227</v>
       </c>
       <c r="K741" s="6" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="L741" s="6" t="s">
         <v>741</v>
@@ -44440,22 +44450,22 @@
     </row>
     <row r="742" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A742" s="5">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B742" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C742" s="6" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="E742" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F742" s="6" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G742" s="6" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H742" s="6" t="s">
         <v>1045</v>
@@ -44464,10 +44474,10 @@
         <v>470</v>
       </c>
       <c r="J742" s="6" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K742" s="6" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="L742" s="6" t="s">
         <v>741</v>
@@ -44481,22 +44491,22 @@
     </row>
     <row r="743" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A743" s="5">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B743" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C743" s="6" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E743" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F743" s="6" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G743" s="6" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H743" s="6" t="s">
         <v>1045</v>
@@ -44505,10 +44515,10 @@
         <v>470</v>
       </c>
       <c r="J743" s="6" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="K743" s="6" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="L743" s="6" t="s">
         <v>741</v>
@@ -44522,34 +44532,34 @@
     </row>
     <row r="744" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A744" s="5">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B744" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>1179</v>
+        <v>976</v>
       </c>
       <c r="E744" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F744" s="6" t="s">
-        <v>1198</v>
+        <v>1177</v>
       </c>
       <c r="G744" s="6" t="s">
-        <v>1220</v>
+        <v>1177</v>
       </c>
       <c r="H744" s="6" t="s">
-        <v>1221</v>
+        <v>1045</v>
       </c>
       <c r="I744" s="6" t="s">
-        <v>812</v>
+        <v>470</v>
       </c>
       <c r="J744" s="6" t="s">
-        <v>1181</v>
+        <v>1156</v>
       </c>
       <c r="K744" s="6" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="L744" s="6" t="s">
         <v>741</v>
@@ -44563,22 +44573,22 @@
     </row>
     <row r="745" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A745" s="5">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B745" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C745" s="6" t="s">
-        <v>1222</v>
+        <v>1179</v>
       </c>
       <c r="E745" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F745" s="6" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G745" s="6" t="s">
-        <v>1204</v>
+        <v>1220</v>
       </c>
       <c r="H745" s="6" t="s">
         <v>1221</v>
@@ -44587,10 +44597,10 @@
         <v>812</v>
       </c>
       <c r="J745" s="6" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="K745" s="6" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="L745" s="6" t="s">
         <v>741</v>
@@ -44604,22 +44614,22 @@
     </row>
     <row r="746" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A746" s="5">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B746" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C746" s="6" t="s">
-        <v>1180</v>
+        <v>1222</v>
       </c>
       <c r="E746" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F746" s="6" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G746" s="6" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H746" s="6" t="s">
         <v>1221</v>
@@ -44628,10 +44638,10 @@
         <v>812</v>
       </c>
       <c r="J746" s="6" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="K746" s="6" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="L746" s="6" t="s">
         <v>741</v>
@@ -44645,22 +44655,22 @@
     </row>
     <row r="747" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A747" s="5">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B747" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C747" s="6" t="s">
-        <v>1223</v>
+        <v>1180</v>
       </c>
       <c r="E747" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F747" s="6" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G747" s="6" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H747" s="6" t="s">
         <v>1221</v>
@@ -44669,10 +44679,10 @@
         <v>812</v>
       </c>
       <c r="J747" s="6" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="K747" s="6" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="L747" s="6" t="s">
         <v>741</v>
@@ -44686,22 +44696,22 @@
     </row>
     <row r="748" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A748" s="5">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B748" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C748" s="6" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E748" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F748" s="6" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G748" s="6" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H748" s="6" t="s">
         <v>1221</v>
@@ -44710,10 +44720,10 @@
         <v>812</v>
       </c>
       <c r="J748" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K748" s="6" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="L748" s="6" t="s">
         <v>741</v>
@@ -44727,22 +44737,22 @@
     </row>
     <row r="749" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A749" s="5">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B749" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C749" s="6" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E749" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F749" s="6" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G749" s="6" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H749" s="6" t="s">
         <v>1221</v>
@@ -44751,10 +44761,10 @@
         <v>812</v>
       </c>
       <c r="J749" s="6" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="K749" s="6" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="L749" s="6" t="s">
         <v>741</v>
@@ -44768,22 +44778,22 @@
     </row>
     <row r="750" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A750" s="5">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B750" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C750" s="6" t="s">
-        <v>436</v>
+        <v>1225</v>
       </c>
       <c r="E750" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F750" s="6" t="s">
-        <v>1342</v>
+        <v>1203</v>
       </c>
       <c r="G750" s="6" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H750" s="6" t="s">
         <v>1221</v>
@@ -44792,10 +44802,10 @@
         <v>812</v>
       </c>
       <c r="J750" s="6" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="K750" s="6" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="L750" s="6" t="s">
         <v>741</v>
@@ -44809,22 +44819,22 @@
     </row>
     <row r="751" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A751" s="5">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B751" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C751" s="6" t="s">
-        <v>969</v>
+        <v>436</v>
       </c>
       <c r="E751" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F751" s="6" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G751" s="6" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H751" s="6" t="s">
         <v>1221</v>
@@ -44833,10 +44843,10 @@
         <v>812</v>
       </c>
       <c r="J751" s="6" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="K751" s="6" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="L751" s="6" t="s">
         <v>741</v>
@@ -44850,22 +44860,22 @@
     </row>
     <row r="752" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A752" s="5">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B752" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C752" s="6" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E752" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F752" s="6" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="G752" s="6" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H752" s="6" t="s">
         <v>1221</v>
@@ -44874,10 +44884,10 @@
         <v>812</v>
       </c>
       <c r="J752" s="6" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="K752" s="6" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="L752" s="6" t="s">
         <v>741</v>
@@ -44891,22 +44901,22 @@
     </row>
     <row r="753" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A753" s="5">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B753" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C753" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E753" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F753" s="6" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G753" s="6" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H753" s="6" t="s">
         <v>1221</v>
@@ -44915,10 +44925,10 @@
         <v>812</v>
       </c>
       <c r="J753" s="6" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K753" s="6" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="L753" s="6" t="s">
         <v>741</v>
@@ -44932,22 +44942,22 @@
     </row>
     <row r="754" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A754" s="5">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B754" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C754" s="6" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E754" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F754" s="6" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G754" s="6" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H754" s="6" t="s">
         <v>1221</v>
@@ -44956,10 +44966,10 @@
         <v>812</v>
       </c>
       <c r="J754" s="6" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K754" s="6" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="L754" s="6" t="s">
         <v>741</v>
@@ -44973,22 +44983,22 @@
     </row>
     <row r="755" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A755" s="5">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B755" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C755" s="6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E755" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F755" s="6" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G755" s="6" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H755" s="6" t="s">
         <v>1221</v>
@@ -44997,10 +45007,10 @@
         <v>812</v>
       </c>
       <c r="J755" s="6" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K755" s="6" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="L755" s="6" t="s">
         <v>741</v>
@@ -45014,22 +45024,22 @@
     </row>
     <row r="756" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A756" s="5">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B756" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C756" s="6" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E756" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F756" s="6" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G756" s="6" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H756" s="6" t="s">
         <v>1221</v>
@@ -45038,10 +45048,10 @@
         <v>812</v>
       </c>
       <c r="J756" s="6" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="K756" s="6" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="L756" s="6" t="s">
         <v>741</v>
@@ -45055,22 +45065,22 @@
     </row>
     <row r="757" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A757" s="5">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B757" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C757" s="6" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E757" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F757" s="6" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G757" s="6" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H757" s="6" t="s">
         <v>1221</v>
@@ -45079,10 +45089,10 @@
         <v>812</v>
       </c>
       <c r="J757" s="6" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="K757" s="6" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="L757" s="6" t="s">
         <v>741</v>
@@ -45096,22 +45106,22 @@
     </row>
     <row r="758" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A758" s="5">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B758" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C758" s="6" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E758" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F758" s="6" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G758" s="6" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H758" s="6" t="s">
         <v>1221</v>
@@ -45120,10 +45130,10 @@
         <v>812</v>
       </c>
       <c r="J758" s="6" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="K758" s="6" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="L758" s="6" t="s">
         <v>741</v>
@@ -45137,22 +45147,22 @@
     </row>
     <row r="759" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A759" s="5">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B759" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C759" s="6" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E759" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F759" s="6" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="G759" s="6" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H759" s="6" t="s">
         <v>1221</v>
@@ -45161,10 +45171,10 @@
         <v>812</v>
       </c>
       <c r="J759" s="6" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="K759" s="6" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="L759" s="6" t="s">
         <v>741</v>
@@ -45178,22 +45188,22 @@
     </row>
     <row r="760" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A760" s="5">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B760" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C760" s="6" t="s">
-        <v>469</v>
+        <v>976</v>
       </c>
       <c r="E760" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F760" s="6" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G760" s="6" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H760" s="6" t="s">
         <v>1221</v>
@@ -45202,10 +45212,10 @@
         <v>812</v>
       </c>
       <c r="J760" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="K760" s="6" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="L760" s="6" t="s">
         <v>741</v>
@@ -45219,34 +45229,34 @@
     </row>
     <row r="761" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A761" s="5">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B761" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C761" s="6" t="s">
-        <v>1179</v>
+        <v>469</v>
       </c>
       <c r="E761" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F761" s="6" t="s">
-        <v>1233</v>
+        <v>1352</v>
       </c>
       <c r="G761" s="6" t="s">
-        <v>1233</v>
+        <v>1219</v>
       </c>
       <c r="H761" s="6" t="s">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="I761" s="6" t="s">
-        <v>133</v>
+        <v>812</v>
       </c>
       <c r="J761" s="6" t="s">
-        <v>1290</v>
+        <v>1197</v>
       </c>
       <c r="K761" s="6" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="L761" s="6" t="s">
         <v>741</v>
@@ -45260,22 +45270,22 @@
     </row>
     <row r="762" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A762" s="5">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B762" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C762" s="6" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E762" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F762" s="6" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G762" s="6" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H762" s="6" t="s">
         <v>1231</v>
@@ -45284,10 +45294,10 @@
         <v>133</v>
       </c>
       <c r="J762" s="6" t="s">
-        <v>1235</v>
+        <v>1290</v>
       </c>
       <c r="K762" s="6" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="L762" s="6" t="s">
         <v>741</v>
@@ -45301,7 +45311,7 @@
     </row>
     <row r="763" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A763" s="5">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B763" s="6" t="s">
         <v>446</v>
@@ -45313,10 +45323,10 @@
         <v>128</v>
       </c>
       <c r="F763" s="6" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="G763" s="6" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H763" s="6" t="s">
         <v>1231</v>
@@ -45325,10 +45335,10 @@
         <v>133</v>
       </c>
       <c r="J763" s="6" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="K763" s="6" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="L763" s="6" t="s">
         <v>741</v>
@@ -45342,22 +45352,22 @@
     </row>
     <row r="764" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A764" s="5">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B764" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C764" s="6" t="s">
-        <v>1232</v>
+        <v>1180</v>
       </c>
       <c r="E764" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F764" s="6" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="G764" s="6" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="H764" s="6" t="s">
         <v>1231</v>
@@ -45366,10 +45376,10 @@
         <v>133</v>
       </c>
       <c r="J764" s="6" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="K764" s="6" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="L764" s="6" t="s">
         <v>741</v>
@@ -45383,25 +45393,22 @@
     </row>
     <row r="765" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A765" s="5">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B765" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C765" s="6" t="s">
-        <v>974</v>
-      </c>
-      <c r="D765" s="6" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="E765" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F765" s="6" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G765" s="6" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="H765" s="6" t="s">
         <v>1231</v>
@@ -45410,10 +45417,10 @@
         <v>133</v>
       </c>
       <c r="J765" s="6" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="K765" s="6" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="L765" s="6" t="s">
         <v>741</v>
@@ -45427,25 +45434,25 @@
     </row>
     <row r="766" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A766" s="5">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B766" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C766" s="6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D766" s="6" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="E766" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F766" s="6" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="G766" s="6" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="H766" s="6" t="s">
         <v>1231</v>
@@ -45454,10 +45461,10 @@
         <v>133</v>
       </c>
       <c r="J766" s="6" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="K766" s="6" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="L766" s="6" t="s">
         <v>741</v>
@@ -45471,25 +45478,25 @@
     </row>
     <row r="767" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A767" s="5">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B767" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C767" s="6" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D767" s="6" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="E767" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F767" s="6" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="G767" s="6" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="H767" s="6" t="s">
         <v>1231</v>
@@ -45498,10 +45505,10 @@
         <v>133</v>
       </c>
       <c r="J767" s="6" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="K767" s="6" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="L767" s="6" t="s">
         <v>741</v>
@@ -45515,25 +45522,25 @@
     </row>
     <row r="768" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A768" s="5">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B768" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C768" s="6" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D768" s="6" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="E768" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F768" s="6" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="G768" s="6" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="H768" s="6" t="s">
         <v>1231</v>
@@ -45542,10 +45549,10 @@
         <v>133</v>
       </c>
       <c r="J768" s="6" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="K768" s="6" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="L768" s="6" t="s">
         <v>741</v>
@@ -45559,25 +45566,25 @@
     </row>
     <row r="769" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A769" s="5">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B769" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C769" s="6" t="s">
-        <v>469</v>
+        <v>970</v>
       </c>
       <c r="D769" s="6" t="s">
-        <v>469</v>
+        <v>1249</v>
       </c>
       <c r="E769" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F769" s="6" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="G769" s="6" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H769" s="6" t="s">
         <v>1231</v>
@@ -45586,10 +45593,10 @@
         <v>133</v>
       </c>
       <c r="J769" s="6" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="K769" s="6" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L769" s="6" t="s">
         <v>741</v>
@@ -45603,25 +45610,25 @@
     </row>
     <row r="770" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A770" s="5">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B770" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C770" s="6" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="D770" s="6" t="s">
-        <v>1254</v>
+        <v>469</v>
       </c>
       <c r="E770" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F770" s="6" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G770" s="6" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="H770" s="6" t="s">
         <v>1231</v>
@@ -45630,10 +45637,10 @@
         <v>133</v>
       </c>
       <c r="J770" s="6" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="K770" s="6" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="L770" s="6" t="s">
         <v>741</v>
@@ -45647,25 +45654,25 @@
     </row>
     <row r="771" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A771" s="5">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B771" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C771" s="6" t="s">
-        <v>974</v>
+        <v>436</v>
       </c>
       <c r="D771" s="6" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="E771" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F771" s="6" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G771" s="6" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="H771" s="6" t="s">
         <v>1231</v>
@@ -45674,10 +45681,10 @@
         <v>133</v>
       </c>
       <c r="J771" s="6" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="K771" s="6" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="L771" s="6" t="s">
         <v>741</v>
@@ -45691,25 +45698,25 @@
     </row>
     <row r="772" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A772" s="5">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B772" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C772" s="6" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D772" s="6" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="E772" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F772" s="6" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="G772" s="6" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="H772" s="6" t="s">
         <v>1231</v>
@@ -45718,10 +45725,10 @@
         <v>133</v>
       </c>
       <c r="J772" s="6" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="K772" s="6" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="L772" s="6" t="s">
         <v>741</v>
@@ -45735,25 +45742,25 @@
     </row>
     <row r="773" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A773" s="5">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B773" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C773" s="6" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D773" s="6" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="E773" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F773" s="6" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G773" s="6" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="H773" s="6" t="s">
         <v>1231</v>
@@ -45762,10 +45769,10 @@
         <v>133</v>
       </c>
       <c r="J773" s="6" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="K773" s="6" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="L773" s="6" t="s">
         <v>741</v>
@@ -45779,25 +45786,25 @@
     </row>
     <row r="774" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A774" s="5">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B774" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C774" s="6" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D774" s="6" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="E774" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F774" s="6" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="G774" s="6" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="H774" s="6" t="s">
         <v>1231</v>
@@ -45806,10 +45813,10 @@
         <v>133</v>
       </c>
       <c r="J774" s="6" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="K774" s="6" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="L774" s="6" t="s">
         <v>741</v>
@@ -45823,25 +45830,25 @@
     </row>
     <row r="775" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A775" s="5">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B775" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C775" s="6" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="D775" s="6" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="E775" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F775" s="6" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="G775" s="6" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="H775" s="6" t="s">
         <v>1231</v>
@@ -45850,10 +45857,10 @@
         <v>133</v>
       </c>
       <c r="J775" s="6" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="K775" s="6" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="L775" s="6" t="s">
         <v>741</v>
@@ -45867,7 +45874,7 @@
     </row>
     <row r="776" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A776" s="5">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B776" s="6" t="s">
         <v>446</v>
@@ -45876,16 +45883,16 @@
         <v>969</v>
       </c>
       <c r="D776" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="E776" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F776" s="6" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="G776" s="6" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="H776" s="6" t="s">
         <v>1231</v>
@@ -45894,10 +45901,10 @@
         <v>133</v>
       </c>
       <c r="J776" s="6" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="K776" s="6" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="L776" s="6" t="s">
         <v>741</v>
@@ -45911,25 +45918,25 @@
     </row>
     <row r="777" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A777" s="5">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B777" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C777" s="6" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D777" s="6" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="E777" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F777" s="6" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="G777" s="6" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="H777" s="6" t="s">
         <v>1231</v>
@@ -45938,10 +45945,10 @@
         <v>133</v>
       </c>
       <c r="J777" s="6" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="K777" s="6" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="L777" s="6" t="s">
         <v>741</v>
@@ -45955,7 +45962,7 @@
     </row>
     <row r="778" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A778" s="5">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B778" s="6" t="s">
         <v>446</v>
@@ -45964,16 +45971,16 @@
         <v>970</v>
       </c>
       <c r="D778" s="6" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="E778" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F778" s="6" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="G778" s="6" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H778" s="6" t="s">
         <v>1231</v>
@@ -45982,10 +45989,10 @@
         <v>133</v>
       </c>
       <c r="J778" s="6" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="K778" s="6" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="L778" s="6" t="s">
         <v>741</v>
@@ -45999,7 +46006,7 @@
     </row>
     <row r="779" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A779" s="5">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B779" s="6" t="s">
         <v>446</v>
@@ -46008,16 +46015,16 @@
         <v>970</v>
       </c>
       <c r="D779" s="6" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="E779" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F779" s="6" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="G779" s="6" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="H779" s="6" t="s">
         <v>1231</v>
@@ -46026,10 +46033,10 @@
         <v>133</v>
       </c>
       <c r="J779" s="6" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="K779" s="6" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="L779" s="6" t="s">
         <v>741</v>
@@ -46043,25 +46050,25 @@
     </row>
     <row r="780" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A780" s="5">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B780" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C780" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D780" s="6" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="E780" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F780" s="6" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="G780" s="6" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="H780" s="6" t="s">
         <v>1231</v>
@@ -46070,10 +46077,10 @@
         <v>133</v>
       </c>
       <c r="J780" s="6" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="K780" s="6" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="L780" s="6" t="s">
         <v>741</v>
@@ -46087,25 +46094,25 @@
     </row>
     <row r="781" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A781" s="5">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B781" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C781" s="6" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D781" s="6" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="E781" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F781" s="6" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="G781" s="6" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H781" s="6" t="s">
         <v>1231</v>
@@ -46114,10 +46121,10 @@
         <v>133</v>
       </c>
       <c r="J781" s="6" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="K781" s="6" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="L781" s="6" t="s">
         <v>741</v>
@@ -46131,34 +46138,37 @@
     </row>
     <row r="782" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A782" s="5">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B782" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C782" s="6" t="s">
-        <v>1180</v>
+        <v>975</v>
+      </c>
+      <c r="D782" s="6" t="s">
+        <v>1287</v>
       </c>
       <c r="E782" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F782" s="6" t="s">
-        <v>1313</v>
+        <v>1288</v>
       </c>
       <c r="G782" s="6" t="s">
-        <v>1327</v>
+        <v>1288</v>
       </c>
       <c r="H782" s="6" t="s">
-        <v>505</v>
+        <v>1231</v>
       </c>
       <c r="I782" s="6" t="s">
-        <v>286</v>
+        <v>133</v>
       </c>
       <c r="J782" s="6" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="K782" s="6" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="L782" s="6" t="s">
         <v>741</v>
@@ -46172,7 +46182,7 @@
     </row>
     <row r="783" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A783" s="5">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B783" s="6" t="s">
         <v>446</v>
@@ -46184,22 +46194,22 @@
         <v>128</v>
       </c>
       <c r="F783" s="6" t="s">
-        <v>1292</v>
+        <v>1313</v>
       </c>
       <c r="G783" s="6" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H783" s="6" t="s">
-        <v>1292</v>
+        <v>505</v>
       </c>
       <c r="I783" s="6" t="s">
         <v>286</v>
       </c>
       <c r="J783" s="6" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="K783" s="6" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="L783" s="6" t="s">
         <v>741</v>
@@ -46213,22 +46223,22 @@
     </row>
     <row r="784" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A784" s="5">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B784" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C784" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E784" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F784" s="6" t="s">
-        <v>1314</v>
+        <v>1292</v>
       </c>
       <c r="G784" s="6" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H784" s="6" t="s">
         <v>1292</v>
@@ -46237,10 +46247,10 @@
         <v>286</v>
       </c>
       <c r="J784" s="6" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="K784" s="6" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="L784" s="6" t="s">
         <v>741</v>
@@ -46254,34 +46264,34 @@
     </row>
     <row r="785" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A785" s="5">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B785" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C785" s="6" t="s">
-        <v>1232</v>
+        <v>1179</v>
       </c>
       <c r="E785" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F785" s="6" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G785" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H785" s="6" t="s">
-        <v>505</v>
+        <v>1292</v>
       </c>
       <c r="I785" s="6" t="s">
         <v>286</v>
       </c>
       <c r="J785" s="6" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="K785" s="6" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="L785" s="6" t="s">
         <v>741</v>
@@ -46295,22 +46305,22 @@
     </row>
     <row r="786" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A786" s="5">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B786" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C786" s="6" t="s">
-        <v>436</v>
+        <v>1232</v>
       </c>
       <c r="E786" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F786" s="6" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="G786" s="6" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H786" s="6" t="s">
         <v>505</v>
@@ -46319,10 +46329,10 @@
         <v>286</v>
       </c>
       <c r="J786" s="6" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="K786" s="6" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="L786" s="6" t="s">
         <v>741</v>
@@ -46336,22 +46346,22 @@
     </row>
     <row r="787" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A787" s="5">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B787" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C787" s="6" t="s">
-        <v>969</v>
+        <v>436</v>
       </c>
       <c r="E787" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F787" s="6" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G787" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H787" s="6" t="s">
         <v>505</v>
@@ -46360,10 +46370,10 @@
         <v>286</v>
       </c>
       <c r="J787" s="6" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="K787" s="6" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="L787" s="6" t="s">
         <v>741</v>
@@ -46377,22 +46387,22 @@
     </row>
     <row r="788" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A788" s="5">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B788" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C788" s="6" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E788" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F788" s="6" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G788" s="6" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H788" s="6" t="s">
         <v>505</v>
@@ -46401,10 +46411,10 @@
         <v>286</v>
       </c>
       <c r="J788" s="6" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="K788" s="6" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="L788" s="6" t="s">
         <v>741</v>
@@ -46418,22 +46428,22 @@
     </row>
     <row r="789" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A789" s="5">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B789" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C789" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E789" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F789" s="6" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G789" s="6" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H789" s="6" t="s">
         <v>505</v>
@@ -46442,10 +46452,10 @@
         <v>286</v>
       </c>
       <c r="J789" s="6" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="K789" s="6" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="L789" s="6" t="s">
         <v>741</v>
@@ -46459,22 +46469,22 @@
     </row>
     <row r="790" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A790" s="5">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B790" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C790" s="6" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E790" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F790" s="6" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="G790" s="6" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H790" s="6" t="s">
         <v>505</v>
@@ -46483,10 +46493,10 @@
         <v>286</v>
       </c>
       <c r="J790" s="6" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="K790" s="6" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="L790" s="6" t="s">
         <v>741</v>
@@ -46500,22 +46510,22 @@
     </row>
     <row r="791" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A791" s="5">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B791" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C791" s="6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E791" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F791" s="6" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G791" s="6" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H791" s="6" t="s">
         <v>505</v>
@@ -46524,10 +46534,10 @@
         <v>286</v>
       </c>
       <c r="J791" s="6" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="K791" s="6" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="L791" s="6" t="s">
         <v>741</v>
@@ -46541,22 +46551,22 @@
     </row>
     <row r="792" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A792" s="5">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B792" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C792" s="6" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E792" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F792" s="6" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="G792" s="6" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H792" s="6" t="s">
         <v>505</v>
@@ -46565,10 +46575,10 @@
         <v>286</v>
       </c>
       <c r="J792" s="6" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="K792" s="6" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="L792" s="6" t="s">
         <v>741</v>
@@ -46582,22 +46592,22 @@
     </row>
     <row r="793" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A793" s="5">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B793" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C793" s="6" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E793" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F793" s="6" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G793" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H793" s="6" t="s">
         <v>505</v>
@@ -46606,10 +46616,10 @@
         <v>286</v>
       </c>
       <c r="J793" s="6" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="K793" s="6" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="L793" s="6" t="s">
         <v>741</v>
@@ -46623,22 +46633,22 @@
     </row>
     <row r="794" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A794" s="5">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B794" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C794" s="6" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E794" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F794" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="G794" s="6" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H794" s="6" t="s">
         <v>505</v>
@@ -46647,10 +46657,10 @@
         <v>286</v>
       </c>
       <c r="J794" s="6" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="K794" s="6" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="L794" s="6" t="s">
         <v>741</v>
@@ -46664,22 +46674,22 @@
     </row>
     <row r="795" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A795" s="5">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B795" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C795" s="6" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E795" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F795" s="6" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G795" s="6" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H795" s="6" t="s">
         <v>505</v>
@@ -46688,10 +46698,10 @@
         <v>286</v>
       </c>
       <c r="J795" s="6" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="K795" s="6" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="L795" s="6" t="s">
         <v>741</v>
@@ -46705,22 +46715,22 @@
     </row>
     <row r="796" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A796" s="5">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B796" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C796" s="6" t="s">
-        <v>469</v>
+        <v>976</v>
       </c>
       <c r="E796" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F796" s="6" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G796" s="6" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H796" s="6" t="s">
         <v>505</v>
@@ -46729,10 +46739,10 @@
         <v>286</v>
       </c>
       <c r="J796" s="6" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="K796" s="6" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="L796" s="6" t="s">
         <v>741</v>
@@ -46746,34 +46756,34 @@
     </row>
     <row r="797" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A797" s="5">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B797" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C797" s="6" t="s">
-        <v>1180</v>
+        <v>469</v>
       </c>
       <c r="E797" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F797" s="6" t="s">
-        <v>1295</v>
+        <v>1326</v>
       </c>
       <c r="G797" s="6" t="s">
-        <v>1295</v>
+        <v>1341</v>
       </c>
       <c r="H797" s="6" t="s">
-        <v>1295</v>
+        <v>505</v>
       </c>
       <c r="I797" s="6" t="s">
-        <v>1296</v>
+        <v>286</v>
       </c>
       <c r="J797" s="6" t="s">
-        <v>1297</v>
+        <v>1312</v>
       </c>
       <c r="K797" s="6" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="L797" s="6" t="s">
         <v>741</v>
@@ -46787,25 +46797,22 @@
     </row>
     <row r="798" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A798" s="5">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B798" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C798" s="6" t="s">
-        <v>975</v>
-      </c>
-      <c r="D798" s="6" t="s">
-        <v>1298</v>
+        <v>1180</v>
       </c>
       <c r="E798" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F798" s="6" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="G798" s="6" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="H798" s="6" t="s">
         <v>1295</v>
@@ -46814,10 +46821,10 @@
         <v>1296</v>
       </c>
       <c r="J798" s="6" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="K798" s="6" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="L798" s="6" t="s">
         <v>741</v>
@@ -46831,34 +46838,37 @@
     </row>
     <row r="799" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A799" s="5">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B799" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C799" s="6" t="s">
-        <v>1180</v>
+        <v>975</v>
+      </c>
+      <c r="D799" s="6" t="s">
+        <v>1298</v>
       </c>
       <c r="E799" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F799" s="6" t="s">
-        <v>1355</v>
+        <v>1299</v>
       </c>
       <c r="G799" s="6" t="s">
-        <v>1356</v>
+        <v>1299</v>
       </c>
       <c r="H799" s="6" t="s">
-        <v>1221</v>
+        <v>1295</v>
       </c>
       <c r="I799" s="6" t="s">
-        <v>812</v>
+        <v>1296</v>
       </c>
       <c r="J799" s="6" t="s">
-        <v>1359</v>
+        <v>1300</v>
       </c>
       <c r="K799" s="6" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="L799" s="6" t="s">
         <v>741</v>
@@ -46872,22 +46882,22 @@
     </row>
     <row r="800" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A800" s="5">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B800" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C800" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E800" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F800" s="6" t="s">
-        <v>1221</v>
+        <v>1355</v>
       </c>
       <c r="G800" s="6" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H800" s="6" t="s">
         <v>1221</v>
@@ -46896,10 +46906,10 @@
         <v>812</v>
       </c>
       <c r="J800" s="6" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="K800" s="6" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="L800" s="6" t="s">
         <v>741</v>
@@ -46913,22 +46923,22 @@
     </row>
     <row r="801" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A801" s="5">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B801" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C801" s="6" t="s">
-        <v>974</v>
+        <v>1179</v>
       </c>
       <c r="E801" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F801" s="6" t="s">
-        <v>1360</v>
+        <v>1221</v>
       </c>
       <c r="G801" s="6" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="H801" s="6" t="s">
         <v>1221</v>
@@ -46937,10 +46947,10 @@
         <v>812</v>
       </c>
       <c r="J801" s="6" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="K801" s="6" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="L801" s="6" t="s">
         <v>741</v>
@@ -46954,22 +46964,22 @@
     </row>
     <row r="802" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A802" s="5">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B802" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C802" s="6" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E802" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F802" s="6" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="G802" s="6" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H802" s="6" t="s">
         <v>1221</v>
@@ -46978,10 +46988,10 @@
         <v>812</v>
       </c>
       <c r="J802" s="6" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="K802" s="6" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="L802" s="6" t="s">
         <v>741</v>
@@ -46995,22 +47005,22 @@
     </row>
     <row r="803" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A803" s="5">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B803" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C803" s="6" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E803" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F803" s="6" t="s">
-        <v>1045</v>
+        <v>1362</v>
       </c>
       <c r="G803" s="6" t="s">
-        <v>1045</v>
+        <v>1362</v>
       </c>
       <c r="H803" s="6" t="s">
         <v>1221</v>
@@ -47019,10 +47029,10 @@
         <v>812</v>
       </c>
       <c r="J803" s="6" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="K803" s="6" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="L803" s="6" t="s">
         <v>741</v>
@@ -47036,22 +47046,22 @@
     </row>
     <row r="804" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A804" s="5">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B804" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C804" s="6" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E804" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F804" s="6" t="s">
-        <v>1365</v>
+        <v>1045</v>
       </c>
       <c r="G804" s="6" t="s">
-        <v>1365</v>
+        <v>1045</v>
       </c>
       <c r="H804" s="6" t="s">
         <v>1221</v>
@@ -47060,10 +47070,10 @@
         <v>812</v>
       </c>
       <c r="J804" s="6" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="K804" s="6" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="L804" s="6" t="s">
         <v>741</v>
@@ -47077,34 +47087,34 @@
     </row>
     <row r="805" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A805" s="5">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B805" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C805" s="6" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E805" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F805" s="6" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="G805" s="6" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="H805" s="6" t="s">
-        <v>1079</v>
+        <v>1221</v>
       </c>
       <c r="I805" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J805" s="6" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="K805" s="6" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="L805" s="6" t="s">
         <v>741</v>
@@ -47118,34 +47128,34 @@
     </row>
     <row r="806" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A806" s="5">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B806" s="6" t="s">
         <v>446</v>
       </c>
       <c r="C806" s="6" t="s">
-        <v>1179</v>
+        <v>970</v>
       </c>
       <c r="E806" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F806" s="6" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="G806" s="6" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="H806" s="6" t="s">
-        <v>1049</v>
+        <v>1079</v>
       </c>
       <c r="I806" s="6" t="s">
         <v>812</v>
       </c>
       <c r="J806" s="6" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="K806" s="6" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="L806" s="6" t="s">
         <v>741</v>
@@ -47159,7 +47169,7 @@
     </row>
     <row r="807" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A807" s="5">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B807" s="6" t="s">
         <v>446</v>
@@ -47171,22 +47181,22 @@
         <v>128</v>
       </c>
       <c r="F807" s="6" t="s">
-        <v>1651</v>
+        <v>1369</v>
       </c>
       <c r="G807" s="6" t="s">
-        <v>1650</v>
+        <v>1370</v>
       </c>
       <c r="H807" s="6" t="s">
-        <v>1649</v>
+        <v>1049</v>
       </c>
       <c r="I807" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J807" s="6" t="s">
-        <v>1652</v>
+        <v>1371</v>
       </c>
       <c r="K807" s="6" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="L807" s="6" t="s">
         <v>741</v>
@@ -47200,7 +47210,7 @@
     </row>
     <row r="808" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A808" s="5">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B808" s="6" t="s">
         <v>446</v>
@@ -47212,22 +47222,22 @@
         <v>128</v>
       </c>
       <c r="F808" s="6" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="G808" s="6" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
       <c r="H808" s="6" t="s">
-        <v>1633</v>
+        <v>1649</v>
       </c>
       <c r="I808" s="6" t="s">
-        <v>1380</v>
+        <v>813</v>
       </c>
       <c r="J808" s="6" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="K808" s="6" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="L808" s="6" t="s">
         <v>741</v>
@@ -47241,7 +47251,7 @@
     </row>
     <row r="809" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A809" s="5">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B809" s="6" t="s">
         <v>446</v>
@@ -47253,22 +47263,22 @@
         <v>128</v>
       </c>
       <c r="F809" s="6" t="s">
-        <v>2043</v>
+        <v>1654</v>
       </c>
       <c r="G809" s="6" t="s">
-        <v>2044</v>
+        <v>1654</v>
       </c>
       <c r="H809" s="6" t="s">
-        <v>2045</v>
+        <v>1633</v>
       </c>
       <c r="I809" s="6" t="s">
-        <v>2046</v>
+        <v>1380</v>
       </c>
       <c r="J809" s="6" t="s">
-        <v>2047</v>
+        <v>1653</v>
       </c>
       <c r="K809" s="6" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="L809" s="6" t="s">
         <v>741</v>
@@ -47282,7 +47292,7 @@
     </row>
     <row r="810" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A810" s="5">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B810" s="6" t="s">
         <v>446</v>
@@ -47294,22 +47304,22 @@
         <v>128</v>
       </c>
       <c r="F810" s="6" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="G810" s="6" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="H810" s="6" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="I810" s="6" t="s">
-        <v>1380</v>
+        <v>2046</v>
       </c>
       <c r="J810" s="6" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
       <c r="K810" s="6" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="L810" s="6" t="s">
         <v>741</v>
@@ -47323,34 +47333,34 @@
     </row>
     <row r="811" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A811" s="5">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B811" s="6" t="s">
-        <v>1655</v>
+        <v>446</v>
       </c>
       <c r="C811" s="6" t="s">
-        <v>1673</v>
+        <v>1179</v>
       </c>
       <c r="E811" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F811" s="6" t="s">
-        <v>1656</v>
+        <v>2048</v>
       </c>
       <c r="G811" s="6" t="s">
-        <v>1656</v>
+        <v>2048</v>
       </c>
       <c r="H811" s="6" t="s">
-        <v>78</v>
+        <v>2049</v>
       </c>
       <c r="I811" s="6" t="s">
-        <v>812</v>
+        <v>1380</v>
       </c>
       <c r="J811" s="6" t="s">
-        <v>1667</v>
+        <v>2050</v>
       </c>
       <c r="K811" s="6" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="L811" s="6" t="s">
         <v>741</v>
@@ -47364,34 +47374,34 @@
     </row>
     <row r="812" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A812" s="5">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B812" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C812" s="6" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="E812" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F812" s="6" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="G812" s="6" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H812" s="6" t="s">
-        <v>1080</v>
+        <v>78</v>
       </c>
       <c r="I812" s="6" t="s">
-        <v>133</v>
+        <v>812</v>
       </c>
       <c r="J812" s="6" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="K812" s="6" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="L812" s="6" t="s">
         <v>741</v>
@@ -47405,34 +47415,34 @@
     </row>
     <row r="813" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A813" s="5">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B813" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C813" s="6" t="s">
-        <v>134</v>
+        <v>1674</v>
       </c>
       <c r="E813" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F813" s="6" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="G813" s="6" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H813" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="I813" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J813" s="6" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="K813" s="6" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="L813" s="6" t="s">
         <v>741</v>
@@ -47446,7 +47456,7 @@
     </row>
     <row r="814" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A814" s="5">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B814" s="6" t="s">
         <v>1655</v>
@@ -47458,22 +47468,22 @@
         <v>128</v>
       </c>
       <c r="F814" s="6" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="G814" s="6" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H814" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="I814" s="6" t="s">
-        <v>813</v>
+        <v>134</v>
       </c>
       <c r="J814" s="6" t="s">
-        <v>1664</v>
+        <v>1669</v>
       </c>
       <c r="K814" s="6" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="L814" s="6" t="s">
         <v>741</v>
@@ -47487,7 +47497,7 @@
     </row>
     <row r="815" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A815" s="5">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B815" s="6" t="s">
         <v>1655</v>
@@ -47499,22 +47509,22 @@
         <v>128</v>
       </c>
       <c r="F815" s="6" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="G815" s="6" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H815" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="I815" s="6" t="s">
-        <v>1644</v>
+        <v>813</v>
       </c>
       <c r="J815" s="6" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="K815" s="6" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="L815" s="6" t="s">
         <v>741</v>
@@ -47528,34 +47538,34 @@
     </row>
     <row r="816" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A816" s="5">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B816" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C816" s="6" t="s">
-        <v>1673</v>
+        <v>134</v>
       </c>
       <c r="E816" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F816" s="6" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="G816" s="6" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H816" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="I816" s="6" t="s">
-        <v>1447</v>
+        <v>1644</v>
       </c>
       <c r="J816" s="6" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="K816" s="6" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="L816" s="6" t="s">
         <v>741</v>
@@ -47569,34 +47579,34 @@
     </row>
     <row r="817" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A817" s="5">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B817" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C817" s="6" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="E817" s="6" t="s">
         <v>128</v>
       </c>
       <c r="F817" s="6" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="G817" s="6" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H817" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="I817" s="6" t="s">
-        <v>1672</v>
+        <v>1447</v>
       </c>
       <c r="J817" s="6" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="K817" s="6" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="L817" s="6" t="s">
         <v>741</v>
@@ -47610,7 +47620,7 @@
     </row>
     <row r="818" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A818" s="5">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B818" s="6" t="s">
         <v>1655</v>
@@ -47622,22 +47632,22 @@
         <v>128</v>
       </c>
       <c r="F818" s="6" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="G818" s="6" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H818" s="6" t="s">
         <v>1080</v>
       </c>
       <c r="I818" s="6" t="s">
-        <v>1405</v>
+        <v>1672</v>
       </c>
       <c r="J818" s="6" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="K818" s="6" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="L818" s="6" t="s">
         <v>741</v>
@@ -47651,37 +47661,37 @@
     </row>
     <row r="819" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A819" s="5">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B819" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C819" s="6" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="E819" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F819" s="6" t="s">
-        <v>1676</v>
+        <v>1663</v>
       </c>
       <c r="G819" s="6" t="s">
-        <v>1676</v>
+        <v>1663</v>
       </c>
       <c r="H819" s="6" t="s">
-        <v>1717</v>
+        <v>1080</v>
       </c>
       <c r="I819" s="6" t="s">
-        <v>470</v>
+        <v>1405</v>
       </c>
       <c r="J819" s="6" t="s">
-        <v>1697</v>
+        <v>1671</v>
       </c>
       <c r="K819" s="6" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="L819" s="6" t="s">
-        <v>1696</v>
+        <v>741</v>
       </c>
       <c r="M819" s="6" t="s">
         <v>389</v>
@@ -47692,7 +47702,7 @@
     </row>
     <row r="820" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A820" s="5">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B820" s="6" t="s">
         <v>1655</v>
@@ -47704,10 +47714,10 @@
         <v>126</v>
       </c>
       <c r="F820" s="6" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="G820" s="6" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H820" s="6" t="s">
         <v>1717</v>
@@ -47716,10 +47726,10 @@
         <v>470</v>
       </c>
       <c r="J820" s="6" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="K820" s="6" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="L820" s="6" t="s">
         <v>1696</v>
@@ -47733,7 +47743,7 @@
     </row>
     <row r="821" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A821" s="5">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B821" s="6" t="s">
         <v>1655</v>
@@ -47745,10 +47755,10 @@
         <v>126</v>
       </c>
       <c r="F821" s="6" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="G821" s="6" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H821" s="6" t="s">
         <v>1717</v>
@@ -47757,10 +47767,10 @@
         <v>470</v>
       </c>
       <c r="J821" s="6" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="K821" s="6" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="L821" s="6" t="s">
         <v>1696</v>
@@ -47774,7 +47784,7 @@
     </row>
     <row r="822" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A822" s="5">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B822" s="6" t="s">
         <v>1655</v>
@@ -47786,10 +47796,10 @@
         <v>126</v>
       </c>
       <c r="F822" s="6" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="G822" s="6" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H822" s="6" t="s">
         <v>1717</v>
@@ -47798,10 +47808,10 @@
         <v>470</v>
       </c>
       <c r="J822" s="6" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="K822" s="6" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="L822" s="6" t="s">
         <v>1696</v>
@@ -47815,7 +47825,7 @@
     </row>
     <row r="823" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A823" s="5">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B823" s="6" t="s">
         <v>1655</v>
@@ -47827,10 +47837,10 @@
         <v>126</v>
       </c>
       <c r="F823" s="6" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="G823" s="6" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H823" s="6" t="s">
         <v>1717</v>
@@ -47839,10 +47849,10 @@
         <v>470</v>
       </c>
       <c r="J823" s="6" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="K823" s="6" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="L823" s="6" t="s">
         <v>1696</v>
@@ -47856,7 +47866,7 @@
     </row>
     <row r="824" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A824" s="5">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B824" s="6" t="s">
         <v>1655</v>
@@ -47868,25 +47878,25 @@
         <v>126</v>
       </c>
       <c r="F824" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="G824" s="6" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H824" s="6" t="s">
         <v>1717</v>
       </c>
       <c r="I824" s="6" t="s">
-        <v>133</v>
+        <v>470</v>
       </c>
       <c r="J824" s="6" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="K824" s="6" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="L824" s="6" t="s">
-        <v>1451</v>
+        <v>1696</v>
       </c>
       <c r="M824" s="6" t="s">
         <v>389</v>
@@ -47897,7 +47907,7 @@
     </row>
     <row r="825" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A825" s="5">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B825" s="6" t="s">
         <v>1655</v>
@@ -47909,10 +47919,10 @@
         <v>126</v>
       </c>
       <c r="F825" s="6" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="G825" s="6" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H825" s="6" t="s">
         <v>1717</v>
@@ -47921,10 +47931,10 @@
         <v>133</v>
       </c>
       <c r="J825" s="6" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="K825" s="6" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="L825" s="6" t="s">
         <v>1451</v>
@@ -47938,7 +47948,7 @@
     </row>
     <row r="826" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A826" s="5">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B826" s="6" t="s">
         <v>1655</v>
@@ -47950,10 +47960,10 @@
         <v>126</v>
       </c>
       <c r="F826" s="6" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="G826" s="6" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H826" s="6" t="s">
         <v>1717</v>
@@ -47962,10 +47972,10 @@
         <v>133</v>
       </c>
       <c r="J826" s="6" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="K826" s="6" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="L826" s="6" t="s">
         <v>1451</v>
@@ -47979,7 +47989,7 @@
     </row>
     <row r="827" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A827" s="5">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B827" s="6" t="s">
         <v>1655</v>
@@ -47991,10 +48001,10 @@
         <v>126</v>
       </c>
       <c r="F827" s="6" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="G827" s="6" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="H827" s="6" t="s">
         <v>1717</v>
@@ -48003,10 +48013,10 @@
         <v>133</v>
       </c>
       <c r="J827" s="6" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="K827" s="6" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="L827" s="6" t="s">
         <v>1451</v>
@@ -48020,7 +48030,7 @@
     </row>
     <row r="828" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A828" s="5">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B828" s="6" t="s">
         <v>1655</v>
@@ -48032,10 +48042,10 @@
         <v>126</v>
       </c>
       <c r="F828" s="6" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G828" s="6" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H828" s="6" t="s">
         <v>1717</v>
@@ -48044,10 +48054,10 @@
         <v>133</v>
       </c>
       <c r="J828" s="6" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="K828" s="6" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="L828" s="6" t="s">
         <v>1451</v>
@@ -48061,37 +48071,37 @@
     </row>
     <row r="829" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A829" s="5">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B829" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C829" s="6" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="E829" s="6" t="s">
         <v>126</v>
       </c>
       <c r="F829" s="6" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="G829" s="6" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="H829" s="6" t="s">
         <v>1717</v>
       </c>
       <c r="I829" s="6" t="s">
-        <v>812</v>
+        <v>133</v>
       </c>
       <c r="J829" s="6" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="K829" s="6" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="L829" s="6" t="s">
-        <v>707</v>
+        <v>1451</v>
       </c>
       <c r="M829" s="6" t="s">
         <v>389</v>
@@ -48102,7 +48112,7 @@
     </row>
     <row r="830" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A830" s="5">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B830" s="6" t="s">
         <v>1655</v>
@@ -48114,10 +48124,10 @@
         <v>126</v>
       </c>
       <c r="F830" s="6" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="G830" s="6" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H830" s="6" t="s">
         <v>1717</v>
@@ -48126,10 +48136,10 @@
         <v>812</v>
       </c>
       <c r="J830" s="6" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="K830" s="6" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="L830" s="6" t="s">
         <v>707</v>
@@ -48143,7 +48153,7 @@
     </row>
     <row r="831" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A831" s="5">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B831" s="6" t="s">
         <v>1655</v>
@@ -48155,10 +48165,10 @@
         <v>126</v>
       </c>
       <c r="F831" s="6" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="G831" s="6" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H831" s="6" t="s">
         <v>1717</v>
@@ -48167,10 +48177,10 @@
         <v>812</v>
       </c>
       <c r="J831" s="6" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="K831" s="6" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="L831" s="6" t="s">
         <v>707</v>
@@ -48184,7 +48194,7 @@
     </row>
     <row r="832" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A832" s="5">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B832" s="6" t="s">
         <v>1655</v>
@@ -48196,10 +48206,10 @@
         <v>126</v>
       </c>
       <c r="F832" s="6" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H832" s="6" t="s">
         <v>1717</v>
@@ -48208,10 +48218,10 @@
         <v>812</v>
       </c>
       <c r="J832" s="6" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="K832" s="6" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="L832" s="6" t="s">
         <v>707</v>
@@ -48225,7 +48235,7 @@
     </row>
     <row r="833" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A833" s="5">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B833" s="6" t="s">
         <v>1655</v>
@@ -48237,10 +48247,10 @@
         <v>126</v>
       </c>
       <c r="F833" s="6" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="G833" s="6" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H833" s="6" t="s">
         <v>1717</v>
@@ -48249,10 +48259,10 @@
         <v>812</v>
       </c>
       <c r="J833" s="6" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="K833" s="6" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="L833" s="6" t="s">
         <v>707</v>
@@ -48266,37 +48276,37 @@
     </row>
     <row r="834" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A834" s="5">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B834" s="6" t="s">
         <v>1655</v>
       </c>
       <c r="C834" s="6" t="s">
-        <v>134</v>
+        <v>1673</v>
       </c>
       <c r="E834" s="6" t="s">
         <v>126</v>
       </c>
       <c r="F834" s="6" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="G834" s="6" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H834" s="6" t="s">
         <v>1717</v>
       </c>
       <c r="I834" s="6" t="s">
-        <v>134</v>
+        <v>812</v>
       </c>
       <c r="J834" s="6" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="K834" s="6" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="L834" s="6" t="s">
-        <v>1452</v>
+        <v>707</v>
       </c>
       <c r="M834" s="6" t="s">
         <v>389</v>
@@ -48307,7 +48317,7 @@
     </row>
     <row r="835" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A835" s="5">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B835" s="6" t="s">
         <v>1655</v>
@@ -48319,10 +48329,10 @@
         <v>126</v>
       </c>
       <c r="F835" s="6" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="G835" s="6" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H835" s="6" t="s">
         <v>1717</v>
@@ -48331,10 +48341,10 @@
         <v>134</v>
       </c>
       <c r="J835" s="6" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="K835" s="6" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="L835" s="6" t="s">
         <v>1452</v>
@@ -48348,7 +48358,7 @@
     </row>
     <row r="836" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A836" s="5">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B836" s="6" t="s">
         <v>1655</v>
@@ -48360,10 +48370,10 @@
         <v>126</v>
       </c>
       <c r="F836" s="6" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="G836" s="6" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H836" s="6" t="s">
         <v>1717</v>
@@ -48372,10 +48382,10 @@
         <v>134</v>
       </c>
       <c r="J836" s="6" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="K836" s="6" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="L836" s="6" t="s">
         <v>1452</v>
@@ -48389,7 +48399,7 @@
     </row>
     <row r="837" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A837" s="5">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B837" s="6" t="s">
         <v>1655</v>
@@ -48401,10 +48411,10 @@
         <v>126</v>
       </c>
       <c r="F837" s="6" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="G837" s="6" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H837" s="6" t="s">
         <v>1717</v>
@@ -48413,10 +48423,10 @@
         <v>134</v>
       </c>
       <c r="J837" s="6" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="K837" s="6" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="L837" s="6" t="s">
         <v>1452</v>
@@ -48430,7 +48440,7 @@
     </row>
     <row r="838" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A838" s="5">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B838" s="6" t="s">
         <v>1655</v>
@@ -48442,10 +48452,10 @@
         <v>126</v>
       </c>
       <c r="F838" s="6" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="G838" s="6" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H838" s="6" t="s">
         <v>1717</v>
@@ -48454,10 +48464,10 @@
         <v>134</v>
       </c>
       <c r="J838" s="6" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="K838" s="6" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="L838" s="6" t="s">
         <v>1452</v>
@@ -48471,51 +48481,48 @@
     </row>
     <row r="839" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A839" s="5">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B839" s="6" t="s">
-        <v>1761</v>
+        <v>1655</v>
       </c>
       <c r="C839" s="6" t="s">
-        <v>2039</v>
+        <v>134</v>
       </c>
       <c r="E839" s="6" t="s">
-        <v>1782</v>
+        <v>126</v>
       </c>
       <c r="F839" s="6" t="s">
-        <v>1762</v>
+        <v>1695</v>
       </c>
       <c r="G839" s="6" t="s">
-        <v>1762</v>
+        <v>1695</v>
       </c>
       <c r="H839" s="6" t="s">
-        <v>1786</v>
+        <v>1717</v>
       </c>
       <c r="I839" s="6" t="s">
-        <v>470</v>
+        <v>134</v>
       </c>
       <c r="J839" s="6" t="s">
-        <v>2051</v>
+        <v>1716</v>
       </c>
       <c r="K839" s="6" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="L839" s="6" t="s">
-        <v>840</v>
+        <v>1452</v>
       </c>
       <c r="M839" s="6" t="s">
         <v>389</v>
       </c>
       <c r="N839" s="6" t="s">
-        <v>1786</v>
-      </c>
-      <c r="O839" s="6" t="s">
-        <v>1787</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="840" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A840" s="5">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B840" s="6" t="s">
         <v>1761</v>
@@ -48527,10 +48534,10 @@
         <v>1782</v>
       </c>
       <c r="F840" s="6" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="G840" s="6" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H840" s="6" t="s">
         <v>1786</v>
@@ -48539,10 +48546,10 @@
         <v>470</v>
       </c>
       <c r="J840" s="6" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="K840" s="6" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="L840" s="6" t="s">
         <v>840</v>
@@ -48559,22 +48566,22 @@
     </row>
     <row r="841" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A841" s="5">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B841" s="6" t="s">
         <v>1761</v>
       </c>
       <c r="C841" s="6" t="s">
-        <v>1055</v>
+        <v>2039</v>
       </c>
       <c r="E841" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="F841" s="6" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="G841" s="6" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H841" s="6" t="s">
         <v>1786</v>
@@ -48583,10 +48590,10 @@
         <v>470</v>
       </c>
       <c r="J841" s="6" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="K841" s="6" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="L841" s="6" t="s">
         <v>840</v>
@@ -48603,7 +48610,7 @@
     </row>
     <row r="842" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A842" s="5">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B842" s="6" t="s">
         <v>1761</v>
@@ -48615,10 +48622,10 @@
         <v>1782</v>
       </c>
       <c r="F842" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="G842" s="6" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H842" s="6" t="s">
         <v>1786</v>
@@ -48627,10 +48634,10 @@
         <v>470</v>
       </c>
       <c r="J842" s="6" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="K842" s="6" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="L842" s="6" t="s">
         <v>840</v>
@@ -48647,7 +48654,7 @@
     </row>
     <row r="843" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A843" s="5">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B843" s="6" t="s">
         <v>1761</v>
@@ -48659,10 +48666,10 @@
         <v>1782</v>
       </c>
       <c r="F843" s="6" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="G843" s="6" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H843" s="6" t="s">
         <v>1786</v>
@@ -48671,10 +48678,10 @@
         <v>470</v>
       </c>
       <c r="J843" s="6" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="K843" s="6" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="L843" s="6" t="s">
         <v>840</v>
@@ -48691,7 +48698,7 @@
     </row>
     <row r="844" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A844" s="5">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B844" s="6" t="s">
         <v>1761</v>
@@ -48703,10 +48710,10 @@
         <v>1782</v>
       </c>
       <c r="F844" s="6" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="G844" s="6" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H844" s="6" t="s">
         <v>1786</v>
@@ -48715,10 +48722,10 @@
         <v>470</v>
       </c>
       <c r="J844" s="6" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="K844" s="6" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="L844" s="6" t="s">
         <v>840</v>
@@ -48735,7 +48742,7 @@
     </row>
     <row r="845" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A845" s="5">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B845" s="6" t="s">
         <v>1761</v>
@@ -48747,10 +48754,10 @@
         <v>1782</v>
       </c>
       <c r="F845" s="6" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="G845" s="6" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H845" s="6" t="s">
         <v>1786</v>
@@ -48759,10 +48766,10 @@
         <v>470</v>
       </c>
       <c r="J845" s="6" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="K845" s="6" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="L845" s="6" t="s">
         <v>840</v>
@@ -48779,7 +48786,7 @@
     </row>
     <row r="846" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A846" s="5">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B846" s="6" t="s">
         <v>1761</v>
@@ -48791,10 +48798,10 @@
         <v>1782</v>
       </c>
       <c r="F846" s="6" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="G846" s="6" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H846" s="6" t="s">
         <v>1786</v>
@@ -48803,10 +48810,10 @@
         <v>470</v>
       </c>
       <c r="J846" s="6" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="K846" s="6" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="L846" s="6" t="s">
         <v>840</v>
@@ -48823,7 +48830,7 @@
     </row>
     <row r="847" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A847" s="5">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B847" s="6" t="s">
         <v>1761</v>
@@ -48835,10 +48842,10 @@
         <v>1782</v>
       </c>
       <c r="F847" s="6" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="G847" s="6" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H847" s="6" t="s">
         <v>1786</v>
@@ -48846,8 +48853,11 @@
       <c r="I847" s="6" t="s">
         <v>470</v>
       </c>
+      <c r="J847" s="6" t="s">
+        <v>2058</v>
+      </c>
       <c r="K847" s="6" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="L847" s="6" t="s">
         <v>840</v>
@@ -48864,22 +48874,22 @@
     </row>
     <row r="848" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A848" s="5">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B848" s="6" t="s">
         <v>1761</v>
       </c>
       <c r="C848" s="6" t="s">
-        <v>2039</v>
+        <v>1055</v>
       </c>
       <c r="E848" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="F848" s="6" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="G848" s="6" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H848" s="6" t="s">
         <v>1786</v>
@@ -48888,7 +48898,7 @@
         <v>470</v>
       </c>
       <c r="K848" s="6" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="L848" s="6" t="s">
         <v>840</v>
@@ -48905,7 +48915,7 @@
     </row>
     <row r="849" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A849" s="5">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B849" s="6" t="s">
         <v>1761</v>
@@ -48917,10 +48927,10 @@
         <v>1782</v>
       </c>
       <c r="F849" s="6" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="G849" s="6" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H849" s="6" t="s">
         <v>1786</v>
@@ -48929,7 +48939,7 @@
         <v>470</v>
       </c>
       <c r="K849" s="6" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="L849" s="6" t="s">
         <v>840</v>
@@ -48946,7 +48956,7 @@
     </row>
     <row r="850" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A850" s="5">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B850" s="6" t="s">
         <v>1761</v>
@@ -48958,10 +48968,10 @@
         <v>1782</v>
       </c>
       <c r="F850" s="6" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="G850" s="6" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H850" s="6" t="s">
         <v>1786</v>
@@ -48970,7 +48980,7 @@
         <v>470</v>
       </c>
       <c r="K850" s="6" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="L850" s="6" t="s">
         <v>840</v>
@@ -48987,22 +48997,22 @@
     </row>
     <row r="851" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A851" s="5">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B851" s="6" t="s">
         <v>1761</v>
       </c>
       <c r="C851" s="6" t="s">
-        <v>1055</v>
+        <v>2039</v>
       </c>
       <c r="E851" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="F851" s="6" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="G851" s="6" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H851" s="6" t="s">
         <v>1786</v>
@@ -49011,7 +49021,7 @@
         <v>470</v>
       </c>
       <c r="K851" s="6" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="L851" s="6" t="s">
         <v>840</v>
@@ -49028,22 +49038,22 @@
     </row>
     <row r="852" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A852" s="5">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B852" s="6" t="s">
         <v>1761</v>
       </c>
       <c r="C852" s="6" t="s">
-        <v>2039</v>
+        <v>1055</v>
       </c>
       <c r="E852" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="F852" s="6" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="G852" s="6" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H852" s="6" t="s">
         <v>1786</v>
@@ -49052,7 +49062,7 @@
         <v>470</v>
       </c>
       <c r="K852" s="6" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="L852" s="6" t="s">
         <v>840</v>
@@ -49069,22 +49079,22 @@
     </row>
     <row r="853" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A853" s="5">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B853" s="6" t="s">
         <v>1761</v>
       </c>
       <c r="C853" s="6" t="s">
-        <v>1055</v>
+        <v>2039</v>
       </c>
       <c r="E853" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="F853" s="6" t="s">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="G853" s="6" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="H853" s="6" t="s">
         <v>1786</v>
@@ -49093,7 +49103,7 @@
         <v>470</v>
       </c>
       <c r="K853" s="6" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="L853" s="6" t="s">
         <v>840</v>
@@ -49110,7 +49120,7 @@
     </row>
     <row r="854" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A854" s="5">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B854" s="6" t="s">
         <v>1761</v>
@@ -49122,10 +49132,10 @@
         <v>1782</v>
       </c>
       <c r="F854" s="6" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="G854" s="6" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H854" s="6" t="s">
         <v>1786</v>
@@ -49134,7 +49144,7 @@
         <v>470</v>
       </c>
       <c r="K854" s="6" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="L854" s="6" t="s">
         <v>840</v>
@@ -49151,22 +49161,22 @@
     </row>
     <row r="855" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A855" s="5">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B855" s="6" t="s">
         <v>1761</v>
       </c>
       <c r="C855" s="6" t="s">
-        <v>2039</v>
+        <v>1055</v>
       </c>
       <c r="E855" s="6" t="s">
         <v>1782</v>
       </c>
       <c r="F855" s="6" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="G855" s="6" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="H855" s="6" t="s">
         <v>1786</v>
@@ -49175,7 +49185,7 @@
         <v>470</v>
       </c>
       <c r="K855" s="6" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="L855" s="6" t="s">
         <v>840</v>
@@ -49192,7 +49202,7 @@
     </row>
     <row r="856" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A856" s="5">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B856" s="6" t="s">
         <v>1761</v>
@@ -49204,10 +49214,10 @@
         <v>1782</v>
       </c>
       <c r="F856" s="6" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="G856" s="6" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H856" s="6" t="s">
         <v>1786</v>
@@ -49216,7 +49226,7 @@
         <v>470</v>
       </c>
       <c r="K856" s="6" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L856" s="6" t="s">
         <v>840</v>
@@ -49233,7 +49243,7 @@
     </row>
     <row r="857" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A857" s="5">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B857" s="6" t="s">
         <v>1761</v>
@@ -49245,19 +49255,19 @@
         <v>1782</v>
       </c>
       <c r="F857" s="6" t="s">
-        <v>1783</v>
+        <v>1777</v>
       </c>
       <c r="G857" s="6" t="s">
-        <v>1783</v>
+        <v>1777</v>
       </c>
       <c r="H857" s="6" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="I857" s="6" t="s">
         <v>470</v>
       </c>
       <c r="K857" s="6" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="L857" s="6" t="s">
         <v>840</v>
@@ -49266,12 +49276,15 @@
         <v>389</v>
       </c>
       <c r="N857" s="6" t="s">
-        <v>1783</v>
+        <v>1786</v>
+      </c>
+      <c r="O857" s="6" t="s">
+        <v>1787</v>
       </c>
     </row>
     <row r="858" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A858" s="5">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B858" s="6" t="s">
         <v>1761</v>
@@ -49280,13 +49293,13 @@
         <v>2039</v>
       </c>
       <c r="E858" s="6" t="s">
-        <v>128</v>
+        <v>1782</v>
       </c>
       <c r="F858" s="6" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="G858" s="6" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="H858" s="6" t="s">
         <v>1783</v>
@@ -49295,10 +49308,10 @@
         <v>470</v>
       </c>
       <c r="K858" s="6" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="L858" s="6" t="s">
-        <v>741</v>
+        <v>840</v>
       </c>
       <c r="M858" s="6" t="s">
         <v>389</v>
@@ -49307,36 +49320,42 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="859" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
+      <c r="A859" s="5">
+        <v>857</v>
+      </c>
       <c r="B859" s="6" t="s">
-        <v>852</v>
+        <v>1761</v>
       </c>
       <c r="C859" s="6" t="s">
-        <v>928</v>
+        <v>2039</v>
       </c>
       <c r="E859" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F859" s="10" t="s">
-        <v>2059</v>
+      <c r="F859" s="6" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G859" s="6" t="s">
+        <v>1785</v>
       </c>
       <c r="H859" s="6" t="s">
-        <v>2062</v>
+        <v>1783</v>
       </c>
       <c r="I859" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J859" s="6" t="s">
-        <v>2063</v>
+        <v>470</v>
+      </c>
+      <c r="K859" s="6" t="s">
+        <v>2461</v>
       </c>
       <c r="L859" s="6" t="s">
         <v>741</v>
       </c>
       <c r="M859" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="O859" s="11" t="s">
-        <v>2066</v>
+        <v>389</v>
+      </c>
+      <c r="N859" s="6" t="s">
+        <v>1783</v>
       </c>
     </row>
     <row r="860" spans="1:15" x14ac:dyDescent="0.3">
@@ -49350,7 +49369,7 @@
         <v>128</v>
       </c>
       <c r="F860" s="10" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="H860" s="6" t="s">
         <v>2062</v>
@@ -49359,7 +49378,7 @@
         <v>812</v>
       </c>
       <c r="J860" s="6" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="L860" s="6" t="s">
         <v>741</v>
@@ -49382,7 +49401,7 @@
         <v>128</v>
       </c>
       <c r="F861" s="10" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="H861" s="6" t="s">
         <v>2062</v>
@@ -49391,7 +49410,7 @@
         <v>812</v>
       </c>
       <c r="J861" s="6" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="L861" s="6" t="s">
         <v>741</v>
@@ -49400,6 +49419,38 @@
         <v>440</v>
       </c>
       <c r="O861" s="11" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="862" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B862" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="C862" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="E862" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F862" s="10" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H862" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="I862" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J862" s="6" t="s">
+        <v>2065</v>
+      </c>
+      <c r="L862" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="M862" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="O862" s="11" t="s">
         <v>2066</v>
       </c>
     </row>
@@ -49407,7 +49458,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="G782:G784 G785:G796" numberStoredAsText="1"/>
+    <ignoredError sqref="G783:G785 G786:G797" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
